--- a/Doc_app/Test_case_ME_IOS.xlsx
+++ b/Doc_app/Test_case_ME_IOS.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="121">
   <si>
     <t>ID</t>
   </si>
@@ -93,57 +93,62 @@
 - Không bị vỡ layout trong trường hợp lage-text mode (accessibility setting) được bật</t>
   </si>
   <si>
-    <t>F_H_01</t>
-  </si>
-  <si>
-    <t>Kiểm tra khả năng điều hướng từ màn Home sang các module khác</t>
+    <t>kiểm thử điều hướng - ID chung: F_H_01</t>
+  </si>
+  <si>
+    <t>F_H_SET</t>
+  </si>
+  <si>
+    <t>Kiểm tra khả năng điều hướng từ màn Home sang module "App Setting"</t>
   </si>
   <si>
     <t>- màn "Home"
 - đã cấp quyền đầy đủ</t>
   </si>
   <si>
-    <t>1.a. chọn button "Setting"</t>
+    <t>1. chọn button "Setting"</t>
   </si>
   <si>
     <t>- chuyển sang màn "Setting"</t>
   </si>
   <si>
-    <t>sub-ID: F_H_SET</t>
-  </si>
-  <si>
-    <t>1.b. điều hướng sang module "Remove objects"bằng 1 trong các cách sau:
-1.b.1. chọn image carousel khi hiện baner "Remove Object"
-1.b.2. chọn button "Remove object" ở fearture compact view
-1.b.3. chọn banner "Remove object" ở topic "AI Tool"
-1.b.4. chọn button "Remove object" ở mục "Rencently Used"(nếu có)</t>
+    <t>F_H_RO</t>
+  </si>
+  <si>
+    <t>Kiểm tra khả năng điều hướng từ màn Home sang module "Remove Object"</t>
+  </si>
+  <si>
+    <t>1. điều hướng sang module "Remove objects"bằng 1 trong các cách sau:
+1.a. chọn image carousel khi hiện baner "Remove Object"
+1.b. chọn button "Remove object" ở fearture compact view
+1.c. chọn banner "Remove object" ở topic "AI Tool"
+1.d. chọn button "Remove object" ở mục "Rencently Used"(nếu có)</t>
   </si>
   <si>
     <t>- hiện dialog "Choose Image"</t>
   </si>
   <si>
-    <t>sub-ID: F_H_RO</t>
-  </si>
-  <si>
-    <t>2.b. chọn 1 ảnh bất kỳ</t>
+    <t>2. chọn 1 ảnh bất kỳ</t>
   </si>
   <si>
     <t>- chuyển sang màn "Remove Objects"
 - ảnh input load thành công, đúng orientation, không xoay sai chiều</t>
   </si>
   <si>
-    <t>1.c. điều hướng sang module "Edit Background"/"Remove Background" bằng 1 trong các cách sau:
-1.c.1. chọn image carousel khi hiện baner "Edit Background"
-1.c.2. chọn button "Edit Background" ở fearture compact view
-1.c.3. chọn banner "Edit Background" ở topic "AI Tool"
-1.c.4. chọn button "Edit Background" ở mục "Recently Used" (nếu có)</t>
-  </si>
-  <si>
-    <t>sub-ID: F_H_RB_01
-- điều hướng:  "Home" -&gt; "Background" Home</t>
-  </si>
-  <si>
-    <t>2.c. chọn 1 ảnh bất kỳ</t>
+    <t>F_H_RB_01</t>
+  </si>
+  <si>
+    <t>Kiểm tra khả năng điều hướng từ màn Home sang module "Edit  Background"</t>
+  </si>
+  <si>
+    <t>1. điều hướng sang module "Edit Background"/"Remove Background" bằng 1 trong các cách sau:
+1.a. chọn image carousel khi hiện baner "Edit Background"
+1.b. chọn button "Edit Background" ở fearture compact view
+1.c. chọn banner "Edit Background" ở topic "AI Tool"
+1.d. chọn button "Edit Background" ở mục "Recently Used" (nếu có)</t>
+  </si>
+  <si>
+    <t>- screen:  "Home" -&gt; "Background" Home</t>
   </si>
   <si>
     <t>- hiện dialog "Processing" -&gt; chuyển sang màn "Background Home"
@@ -161,17 +166,16 @@
     <t>- không có kết nối internet</t>
   </si>
   <si>
-    <t>1.d. chọn 1 template bất kỳ ở topic "Background"</t>
+    <t>F_H_RB_02</t>
+  </si>
+  <si>
+    <t>1. chọn 1 template bất kỳ ở topic "Background"</t>
   </si>
   <si>
     <t>- hiện dialog "Choose image"</t>
   </si>
   <si>
-    <t>sub-ID: F_H_RB_02 
-- điều hướng: "Home" -&gt; "Background Editor"</t>
-  </si>
-  <si>
-    <t>2.d. chọn 1 ảnh bất kỳ</t>
+    <t>- điều hướng: "Home" -&gt; "Background Editor"</t>
   </si>
   <si>
     <t>- hiện dialog "Processing" -&gt; chuyển sang màn "Background Editor"
@@ -179,7 +183,10 @@
 - load thành công, đúng template đã chọn</t>
   </si>
   <si>
-    <t>1.e. chọn 1 tempalate bất kỳ ở topic "Design"</t>
+    <t>F_H_RB_03</t>
+  </si>
+  <si>
+    <t>1. chọn 1 tempalate bất kỳ ở topic "Design"</t>
   </si>
   <si>
     <t>- sang màn "Background Editor"
@@ -187,14 +194,10 @@
 - frontground có button "replace"</t>
   </si>
   <si>
-    <t>sub-ID: F_H_RB_03 
-- điều hướng: "Home" -&gt; "Background Editor"</t>
-  </si>
-  <si>
-    <t>2.e. chọn button "replace"</t>
-  </si>
-  <si>
-    <t>3.e chọn 1 ảnh bất kỳ</t>
+    <t>2. chọn button "replace"</t>
+  </si>
+  <si>
+    <t>3. chọn 1 ảnh bất kỳ</t>
   </si>
   <si>
     <t>- hiện dialog"Processing" -&gt; quay về màn "Background Editor"
@@ -204,17 +207,17 @@
     <t>- hiện modal "Error": check your internet</t>
   </si>
   <si>
-    <t>1.f. điều hướng sang module "Basic Edit" bằng 1 trong các cách sau đây:
-1.f.1. chọn button "Start Editing" trên fearture compact view
-1.f.2. chọn button "Basic Edit" trên fearture compact view
-1.f.3. chọn banner "Basic Edit" ở mục "AI Tools"
-1.f.4. chọn button "Basic Edit" ở mục "Recently used"</t>
-  </si>
-  <si>
-    <t>Sub-ID: F_H_BE_01</t>
-  </si>
-  <si>
-    <t>2.f. chọn 1 ảnh bất kỳ</t>
+    <t>F_H_BE_01</t>
+  </si>
+  <si>
+    <t>Kiểm tra khả năng điều hướng từ màn Home sang module "Basic Edit"</t>
+  </si>
+  <si>
+    <t>1. điều hướng sang module "Basic Edit" bằng 1 trong các cách sau đây:
+1.a. chọn button "Start Editing" trên fearture compact view
+1.b. chọn button "Basic Edit" trên fearture compact view
+1.c. chọn banner "Basic Edit" ở mục "AI Tools"
+1.d. chọn button "Basic Edit" ở mục "Recently used"</t>
   </si>
   <si>
     <t>- sang màn "Basic Edit"
@@ -223,14 +226,11 @@
 - non-pro acount: các tool button "AI Fill", "AI Expand" được đính badge "Pro"</t>
   </si>
   <si>
-    <t>1.g. điều hướng sang module "Basic Edit" với các tool đã được bật sẵn bằng cách chọn các button sau: 
+    <t>F_H_BE_02</t>
+  </si>
+  <si>
+    <t>1. điều hướng sang module "Basic Edit" với các tool đã được bật sẵn bằng cách chọn các button sau: 
 "Frame", "Filter", "Adjust", "Blur", "Texture", "Brushes", "Crop", "Text", "Sticker"</t>
-  </si>
-  <si>
-    <t>sub-ID: F_H_BE_02</t>
-  </si>
-  <si>
-    <t>2.g. chọn 1 ảnh bất kỳ</t>
   </si>
   <si>
     <t>- sang màn "Basic Edit"
@@ -238,17 +238,17 @@
 - tool bottom sheet tương ứng với fearture đã chọn (ở step 1) hiện trên màn hình với 1 option default đã được chọn</t>
   </si>
   <si>
-    <t>1.h. điều hướng sang module "AI Enhance" bằng 1 trong các cách sau: 
-1.h.1. chọn image carousel khi hiện banner "AI Enhance"
-1.h.2. chọn button "AI Enhance" ở fearture compact view 
-1.h.3. chọn banner "AI Enhance" ở mục "AI Tools"
-1.h.4. chọn button "AI Enhance" ở mục "Recently Used" (nếu có)</t>
-  </si>
-  <si>
-    <t>sub-ID: F_H_AE</t>
-  </si>
-  <si>
-    <t>2.h. chọn 1 ảnh bất kỳ</t>
+    <t>F_H_AE</t>
+  </si>
+  <si>
+    <t>Kiểm tra khả năng điều hướng từ màn Home sang module "AI Enhance"</t>
+  </si>
+  <si>
+    <t>1. điều hướng sang module "AI Enhance" bằng 1 trong các cách sau: 
+1.a. chọn image carousel khi hiện banner "AI Enhance"
+1.b. chọn button "AI Enhance" ở fearture compact view 
+1.c. chọn banner "AI Enhance" ở mục "AI Tools"
+1.d. chọn button "AI Enhance" ở mục "Recently Used" (nếu có)</t>
   </si>
   <si>
     <t>- chuyển sang màn "AI Enhance"
@@ -261,7 +261,13 @@
 - hiện modal "Error": check your internet</t>
   </si>
   <si>
-    <t>1.i. chọn button "Collage"</t>
+    <t>F_H_CL</t>
+  </si>
+  <si>
+    <t>Kiểm tra khả năng điều hướng từ màn Home sang module "Collage"</t>
+  </si>
+  <si>
+    <t>1. chọn button "Collage"</t>
   </si>
   <si>
     <t>- sang màn chọn ảnh của module Collage
@@ -269,10 +275,16 @@
 - album default được chọn là "Recent"</t>
   </si>
   <si>
-    <t>sub-ID: F_H_CL</t>
-  </si>
-  <si>
-    <t>1.j.1. chọn button "AI Fill"</t>
+    <t>F_H_AF_NOR</t>
+  </si>
+  <si>
+    <t>Kiểm tra khả năng điều hướng từ màn Home sang module "AI Fill"</t>
+  </si>
+  <si>
+    <t>1. điều hướng sang module "AI Fill" bằng 1 trong số các phương thức sau:
+- chọn button "AI Fill" ở fearture compact view
+- chọn button "AI Fill" ở mục "Recently Used" (nếu có) 
+- chọn banner "AI Fill" tại mục "AI creator"</t>
   </si>
   <si>
     <t>- hiện modal "Try now" của fearture "AI Fill"
@@ -280,20 +292,17 @@
 - layout không bị vỡ/ảnh hưởng khi 'Large text mode' đang được bật</t>
   </si>
   <si>
-    <t>- acount thường</t>
-  </si>
-  <si>
-    <t>2.j.1.a. chọn button "Try now"</t>
+    <t>2.a. chọn button "Try now"</t>
   </si>
   <si>
     <t>- hiện dialog "Chose Image"</t>
   </si>
   <si>
     <t>sub-ID: F_H_AF_NOR_01
-- gồm các step: 1.j.1 -&gt; 2.j.1.a -&gt; 3.j.1.a</t>
-  </si>
-  <si>
-    <t>3.j.1.a. chọn 1 ảnh bất kỳ</t>
+- gồm các step: 1-&gt; 2.a -&gt; 3.a</t>
+  </si>
+  <si>
+    <t>3.a. chọn 1 ảnh bất kỳ</t>
   </si>
   <si>
     <t>- chuyển sang màn "AI Fill"
@@ -302,27 +311,160 @@
 - promt-input text-box trống, chưa có nội dung</t>
   </si>
   <si>
-    <t>2.j.1.b. chọn button "X"</t>
+    <t>2.b. chọn button "X"</t>
   </si>
   <si>
     <t>- ẩn modal "Try now", về màn "Home"</t>
   </si>
   <si>
     <t>sub-ID: F_H_AF_NOR_02
-- gồm các step: 1.j.1 -&gt; 2.j.1.b</t>
-  </si>
-  <si>
-    <t>1.j.2. chọn button "AI Fill"</t>
-  </si>
-  <si>
-    <t>- acount Pro</t>
-  </si>
-  <si>
-    <t>sub-ID:
-F_H_AF_PRO</t>
-  </si>
-  <si>
-    <t>2.j.2 chọn 1 ảnh bất kỳ</t>
+- gồm các step: 1 -&gt; 2.b</t>
+  </si>
+  <si>
+    <t>F_H_AF_PRO</t>
+  </si>
+  <si>
+    <t>1. điều hướng sang module "AI Fill"</t>
+  </si>
+  <si>
+    <t>- account Pro</t>
+  </si>
+  <si>
+    <t>- step 1: truy cập bằng 1 trong số các cách đã nêu ở step 1 tc F_H_AF_NOR</t>
+  </si>
+  <si>
+    <t>F_H_AFT_01</t>
+  </si>
+  <si>
+    <t>Kiểm tra khả năng điều hướng từ màn Home sang module "AI Filter "</t>
+  </si>
+  <si>
+    <t>1. điều hướng sang module AI Fillter bằng 1 trong các cách sau:
+1.a. chọn image carousel khi đang hiện banner "AI Filter" 
+1.b. chọn button "AI Filter" ở fearture compact view 
+1.c. chọn button "AI Filter" ở mục "Recently Used" (nếu có)
+1.d. chọn banner "AI Filter" ở mục "AI creator" 
+1.e. chọn tab "AI Filter" trên tab bar</t>
+  </si>
+  <si>
+    <t>- chuyển sang màn "Choose Style"
+- tab được chọn trên tab bar chuyển sang "AI Filter"
+- Normal (non-pro): các template chỉ dành cho gói pro được đính Badge "Pro"và khóa lại
+- Pro: tất cả các template được mở khóa và không còn Badge "Pro"</t>
+  </si>
+  <si>
+    <t>F_H_AFT_02</t>
+  </si>
+  <si>
+    <t>1. chọn 1 style ở mục "AI Filters"</t>
+  </si>
+  <si>
+    <t>- chuyển sang màn "AI Filter"
+- ảnh input đã được xử lý và gen lại theo style đã chọn</t>
+  </si>
+  <si>
+    <t>F_H_AEX_NOR</t>
+  </si>
+  <si>
+    <t>Kiểm tra khả năng điều hướng từ màn Home sang module "AI Expand"</t>
+  </si>
+  <si>
+    <t>1. điều hướng sang module "AI Expand" bằng 1 trong các cách sau đây: 
+- chọn button "AI Expand"ở fearture compact view
+- chọn button "AI Expand" ở mục "Recently Used" (nếu có)
+- chọn banner "AI Expand" ở mục "AI Tools"</t>
+  </si>
+  <si>
+    <t>- hiện modal "Try now" của fearture "AI Expand"
+- UI modal "Try now" hiển thị đúng theo thiết kế
+- layout không bị vỡ/ảnh hưởng khi 'Large text mode' đang được bật</t>
+  </si>
+  <si>
+    <t>2. chọn button "Try now"</t>
+  </si>
+  <si>
+    <t>- chuyển sang màn "Expand" 
+- ảnh input load thành công, đúng oriantation, không xoay sai chiều</t>
+  </si>
+  <si>
+    <t>F_H_AEX_PRO</t>
+  </si>
+  <si>
+    <t>1. điều hướng sang module "AI Expand"</t>
+  </si>
+  <si>
+    <t>- account pro</t>
+  </si>
+  <si>
+    <t>- step 1: truy cập bằng 1 trong số các cách đã nêu ở step 1 tc F_H_AEX_NOR</t>
+  </si>
+  <si>
+    <t>F_H_AG</t>
+  </si>
+  <si>
+    <t>Kiểm tra khả năng điều hướng từ màn Home sang module "AI Generate"</t>
+  </si>
+  <si>
+    <t>- màn "Home" 
+- đã cấp quyền đầy đủ</t>
+  </si>
+  <si>
+    <t>1. điều hướng sang module "AI Generate" bằng 1 trong các cách sau đây:
+1.a. chọn button "AI Generate" ở fearture compact view
+1.b. chọn tab "AI Generate" ở tab bar 
+1.c. chọn button "AI Generate" ở mục "Recently Used"(nếu có)</t>
+  </si>
+  <si>
+    <t>- chuyển sang màn "Describe"</t>
+  </si>
+  <si>
+    <t>functional test các chức năng còn lại</t>
+  </si>
+  <si>
+    <t>F_H_02</t>
+  </si>
+  <si>
+    <t>kiểm thử chức năng log used-fearture history</t>
+  </si>
+  <si>
+    <t>- màn "Home"</t>
+  </si>
+  <si>
+    <t>1. điều hướng sang 1 fearture bất kỳ</t>
+  </si>
+  <si>
+    <t>- chuyển sang màn hoặc hiển thị các modal ban đầu tương ứng của fearture đó</t>
+  </si>
+  <si>
+    <t>- step1: không cần phải hoàn thành việc điều hướng, chỉ cần chọn button của fearture đó trên màn Home là được</t>
+  </si>
+  <si>
+    <t>2. back về màn "Home"</t>
+  </si>
+  <si>
+    <t>- button của chức nó đó xuất hiện và được đẩy lên thứ tự đầu tiên ở mục "Recently Used"
+- không button chức năng nào bị lặp lại (mỗi fearture chỉ được log 1 lần trong list)</t>
+  </si>
+  <si>
+    <t>F_H_03</t>
+  </si>
+  <si>
+    <t>kiểm thử chức năng link với app "Video Eraser"</t>
+  </si>
+  <si>
+    <t>1. chọn button "Video Object Remover"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- mở "App store" dẫn thẳng đến trang tải app "video eraser" </t>
+  </si>
+  <si>
+    <t>- app "video eraser" chưa được cài đặt</t>
+  </si>
+  <si>
+    <t>- mở app "video eraser"</t>
+  </si>
+  <si>
+    <t>- app "video eraser" đã có trong thiết bị</t>
   </si>
 </sst>
 </file>
@@ -682,7 +824,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="26">
+  <borders count="27">
     <border>
       <left/>
       <right/>
@@ -810,6 +952,30 @@
       <left style="medium">
         <color auto="1"/>
       </left>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
       <right style="medium">
         <color auto="1"/>
       </right>
@@ -862,17 +1028,6 @@
         <color auto="1"/>
       </right>
       <top/>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
@@ -1015,7 +1170,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1027,34 +1182,34 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="25" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="24" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="26" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1139,13 +1294,19 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1153,150 +1314,294 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1832,504 +2137,838 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="6.3828125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="29.5546875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="40.1015625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.015625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="12.109375" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="7.546875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="11.5859375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.375" style="3" customWidth="1"/>
+    <col min="4" max="4" width="29.5546875" style="3" customWidth="1"/>
+    <col min="5" max="5" width="40.1015625" style="3" customWidth="1"/>
+    <col min="6" max="6" width="13.015625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="12.109375" style="3" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1" spans="1:7">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="16" t="s">
+      <c r="G1" s="50" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" ht="17" spans="1:7">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="40" t="s">
+      <c r="C2" s="78" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="41" t="s">
+      <c r="E2" s="79" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="42" t="s">
+      <c r="F2" s="80" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="19"/>
+      <c r="G2" s="51"/>
     </row>
     <row r="3" ht="135" customHeight="1" spans="1:7">
-      <c r="A3" s="7"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="9" t="s">
+      <c r="A3" s="9"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="43" t="s">
+      <c r="E3" s="81" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="20"/>
-      <c r="G3" s="21"/>
+      <c r="F3" s="52"/>
+      <c r="G3" s="53"/>
     </row>
     <row r="4" ht="34" spans="1:7">
-      <c r="A4" s="7"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="9" t="s">
+      <c r="A4" s="9"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="43" t="s">
+      <c r="E4" s="81" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="20"/>
-      <c r="G4" s="21"/>
+      <c r="F4" s="52"/>
+      <c r="G4" s="53"/>
     </row>
     <row r="5" ht="101.75" spans="1:7">
-      <c r="A5" s="10"/>
-      <c r="B5" s="11"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="12" t="s">
+      <c r="A5" s="12"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="44" t="s">
+      <c r="E5" s="82" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="23"/>
-      <c r="G5" s="24"/>
-    </row>
-    <row r="6" ht="135.75" spans="1:7">
-      <c r="A6" s="13" t="s">
+      <c r="F5" s="49"/>
+      <c r="G5" s="54"/>
+    </row>
+    <row r="6" ht="17.55" spans="1:7">
+      <c r="A6" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="16"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="55"/>
+    </row>
+    <row r="7" ht="103" customHeight="1" spans="1:7">
+      <c r="A7" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="45" t="s">
+      <c r="B7" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="C7" s="83" t="s">
         <v>22</v>
       </c>
-      <c r="E6" s="46" t="s">
+      <c r="D7" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="26"/>
-      <c r="G6" s="27" t="s">
+      <c r="E7" s="84" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="7" ht="185" spans="1:7">
-      <c r="A7" s="13"/>
-      <c r="B7" s="13"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="6" t="s">
+      <c r="F7" s="43"/>
+      <c r="G7" s="57"/>
+    </row>
+    <row r="8" ht="185" spans="1:7">
+      <c r="A8" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="E7" s="47" t="s">
+      <c r="B8" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="F7" s="17"/>
-      <c r="G7" s="29" t="s">
+      <c r="C8" s="78" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="8" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="8" ht="51.75" spans="1:7">
-      <c r="A8" s="13"/>
-      <c r="B8" s="13"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="12" t="s">
+      <c r="E8" s="85" t="s">
         <v>28</v>
       </c>
-      <c r="E8" s="48" t="s">
+      <c r="F8" s="45"/>
+      <c r="G8" s="51"/>
+    </row>
+    <row r="9" ht="51.75" spans="1:7">
+      <c r="A9" s="22"/>
+      <c r="B9" s="23"/>
+      <c r="C9" s="13"/>
+      <c r="D9" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="F8" s="22"/>
-      <c r="G8" s="31"/>
-    </row>
-    <row r="9" ht="185" spans="1:7">
-      <c r="A9" s="13"/>
-      <c r="B9" s="13"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="6" t="s">
+      <c r="E9" s="86" t="s">
         <v>30</v>
       </c>
-      <c r="E9" s="47" t="s">
-        <v>26</v>
-      </c>
-      <c r="F9" s="17"/>
-      <c r="G9" s="19" t="s">
+      <c r="F9" s="47"/>
+      <c r="G9" s="54"/>
+    </row>
+    <row r="10" ht="202" spans="1:7">
+      <c r="A10" s="6" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="10" ht="101" spans="1:7">
-      <c r="A10" s="13"/>
-      <c r="B10" s="13"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="9" t="s">
+      <c r="B10" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="E10" s="49" t="s">
+      <c r="C10" s="78" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="F10" s="43" t="s">
+      <c r="E10" s="85" t="s">
+        <v>28</v>
+      </c>
+      <c r="F10" s="45"/>
+      <c r="G10" s="87" t="s">
         <v>34</v>
       </c>
-      <c r="G10" s="21"/>
-    </row>
-    <row r="11" ht="34.75" spans="1:7">
-      <c r="A11" s="13"/>
-      <c r="B11" s="13"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="48" t="s">
+    </row>
+    <row r="11" ht="101" spans="1:7">
+      <c r="A11" s="9"/>
+      <c r="B11" s="24"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="E11" s="88" t="s">
         <v>35</v>
       </c>
-      <c r="F11" s="44" t="s">
+      <c r="F11" s="81" t="s">
         <v>36</v>
       </c>
-      <c r="G11" s="24"/>
-    </row>
-    <row r="12" ht="34" spans="1:7">
-      <c r="A12" s="13"/>
-      <c r="B12" s="13"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="6" t="s">
+      <c r="G11" s="53"/>
+    </row>
+    <row r="12" ht="34.75" spans="1:7">
+      <c r="A12" s="12"/>
+      <c r="B12" s="24"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="86" t="s">
         <v>37</v>
       </c>
-      <c r="E12" s="47" t="s">
+      <c r="F12" s="82" t="s">
         <v>38</v>
       </c>
-      <c r="F12" s="17"/>
-      <c r="G12" s="19" t="s">
+      <c r="G12" s="54"/>
+    </row>
+    <row r="13" ht="34" spans="1:7">
+      <c r="A13" s="6" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="13" ht="68" spans="1:7">
-      <c r="A13" s="13"/>
-      <c r="B13" s="13"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="9" t="s">
+      <c r="B13" s="24"/>
+      <c r="C13" s="78" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="E13" s="49" t="s">
+      <c r="E13" s="85" t="s">
         <v>41</v>
       </c>
-      <c r="F13" s="43" t="s">
-        <v>34</v>
-      </c>
-      <c r="G13" s="21"/>
-    </row>
-    <row r="14" ht="34.75" spans="1:7">
-      <c r="A14" s="13"/>
-      <c r="B14" s="13"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="48" t="s">
-        <v>35</v>
-      </c>
-      <c r="F14" s="44" t="s">
+      <c r="F13" s="45"/>
+      <c r="G13" s="87" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" ht="68" spans="1:7">
+      <c r="A14" s="9"/>
+      <c r="B14" s="24"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="E14" s="88" t="s">
+        <v>43</v>
+      </c>
+      <c r="F14" s="81" t="s">
         <v>36</v>
       </c>
-      <c r="G14" s="24"/>
-    </row>
-    <row r="15" ht="51" spans="1:7">
-      <c r="A15" s="13"/>
-      <c r="B15" s="13"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="6" t="s">
+      <c r="G14" s="53"/>
+    </row>
+    <row r="15" ht="34.75" spans="1:7">
+      <c r="A15" s="12"/>
+      <c r="B15" s="24"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="86" t="s">
+        <v>37</v>
+      </c>
+      <c r="F15" s="82" t="s">
+        <v>38</v>
+      </c>
+      <c r="G15" s="54"/>
+    </row>
+    <row r="16" ht="51" spans="1:7">
+      <c r="A16" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" s="24"/>
+      <c r="C16" s="78" t="s">
+        <v>22</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E16" s="85" t="s">
+        <v>46</v>
+      </c>
+      <c r="F16" s="45"/>
+      <c r="G16" s="87" t="s">
         <v>42</v>
       </c>
-      <c r="E15" s="47" t="s">
-        <v>43</v>
-      </c>
-      <c r="F15" s="17"/>
-      <c r="G15" s="19" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="16" ht="17" spans="1:7">
-      <c r="A16" s="13"/>
-      <c r="B16" s="13"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="E16" s="49" t="s">
-        <v>26</v>
-      </c>
-      <c r="G16" s="21"/>
-    </row>
-    <row r="17" ht="51" spans="1:7">
-      <c r="A17" s="13"/>
-      <c r="B17" s="13"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="E17" s="49" t="s">
+    </row>
+    <row r="17" ht="17" spans="1:7">
+      <c r="A17" s="9"/>
+      <c r="B17" s="24"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="F17" s="43" t="s">
-        <v>34</v>
-      </c>
-      <c r="G17" s="21"/>
-    </row>
-    <row r="18" ht="34.75" spans="1:7">
-      <c r="A18" s="13"/>
-      <c r="B18" s="13"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="48" t="s">
+      <c r="E17" s="88" t="s">
+        <v>28</v>
+      </c>
+      <c r="G17" s="53"/>
+    </row>
+    <row r="18" ht="51" spans="1:7">
+      <c r="A18" s="9"/>
+      <c r="B18" s="24"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="F18" s="44" t="s">
+      <c r="E18" s="88" t="s">
+        <v>49</v>
+      </c>
+      <c r="F18" s="81" t="s">
         <v>36</v>
       </c>
-      <c r="G18" s="24"/>
-    </row>
-    <row r="19" ht="168" spans="1:7">
-      <c r="A19" s="13"/>
-      <c r="B19" s="13"/>
-      <c r="C19" s="8"/>
-      <c r="D19" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="E19" s="47" t="s">
-        <v>26</v>
-      </c>
-      <c r="F19" s="17"/>
-      <c r="G19" s="19" t="s">
+      <c r="G18" s="53"/>
+    </row>
+    <row r="19" ht="34.75" spans="1:7">
+      <c r="A19" s="12"/>
+      <c r="B19" s="23"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="86" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="20" ht="101.75" spans="1:7">
-      <c r="A20" s="13"/>
-      <c r="B20" s="13"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="12" t="s">
+      <c r="F19" s="82" t="s">
+        <v>38</v>
+      </c>
+      <c r="G19" s="54"/>
+    </row>
+    <row r="20" ht="185" spans="1:7">
+      <c r="A20" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="E20" s="48" t="s">
+      <c r="B20" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="F20" s="22"/>
-      <c r="G20" s="24"/>
-    </row>
-    <row r="21" ht="101" spans="1:7">
-      <c r="A21" s="13"/>
-      <c r="B21" s="13"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="6" t="s">
+      <c r="C20" s="78" t="s">
+        <v>22</v>
+      </c>
+      <c r="D20" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="E21" s="47" t="s">
-        <v>26</v>
-      </c>
-      <c r="F21" s="17"/>
-      <c r="G21" s="19" t="s">
+      <c r="E20" s="85" t="s">
+        <v>28</v>
+      </c>
+      <c r="F20" s="45"/>
+      <c r="G20" s="51"/>
+    </row>
+    <row r="21" ht="101.75" spans="1:7">
+      <c r="A21" s="12"/>
+      <c r="B21" s="26"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="E21" s="86" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="22" ht="101.75" spans="1:7">
-      <c r="A22" s="13"/>
-      <c r="B22" s="13"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="12" t="s">
+      <c r="F21" s="47"/>
+      <c r="G21" s="54"/>
+    </row>
+    <row r="22" ht="101" spans="1:7">
+      <c r="A22" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="E22" s="48" t="s">
+      <c r="B22" s="26"/>
+      <c r="C22" s="78" t="s">
+        <v>22</v>
+      </c>
+      <c r="D22" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="F22" s="22"/>
-      <c r="G22" s="24"/>
-    </row>
-    <row r="23" ht="185" spans="1:7">
-      <c r="A23" s="13"/>
-      <c r="B23" s="13"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="6" t="s">
+      <c r="E22" s="85" t="s">
+        <v>28</v>
+      </c>
+      <c r="F22" s="45"/>
+      <c r="G22" s="51"/>
+    </row>
+    <row r="23" ht="101.75" spans="1:7">
+      <c r="A23" s="12"/>
+      <c r="B23" s="27"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="E23" s="86" t="s">
         <v>57</v>
       </c>
-      <c r="E23" s="47" t="s">
-        <v>26</v>
-      </c>
-      <c r="F23" s="17"/>
-      <c r="G23" s="29" t="s">
+      <c r="F23" s="47"/>
+      <c r="G23" s="54"/>
+    </row>
+    <row r="24" ht="185" spans="1:7">
+      <c r="A24" s="6" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="24" ht="110" customHeight="1" spans="1:7">
-      <c r="A24" s="13"/>
-      <c r="B24" s="13"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="9" t="s">
+      <c r="B24" s="25" t="s">
         <v>59</v>
       </c>
-      <c r="E24" s="49" t="s">
+      <c r="C24" s="78" t="s">
+        <v>22</v>
+      </c>
+      <c r="D24" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="F24" s="43" t="s">
-        <v>34</v>
-      </c>
-      <c r="G24" s="33"/>
-    </row>
-    <row r="25" ht="68.75" spans="1:7">
-      <c r="A25" s="13"/>
-      <c r="B25" s="13"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="12"/>
-      <c r="E25" s="48" t="s">
+      <c r="E24" s="85" t="s">
+        <v>28</v>
+      </c>
+      <c r="F24" s="45"/>
+      <c r="G24" s="61"/>
+    </row>
+    <row r="25" ht="110" customHeight="1" spans="1:7">
+      <c r="A25" s="9"/>
+      <c r="B25" s="26"/>
+      <c r="C25" s="10"/>
+      <c r="D25" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="E25" s="88" t="s">
         <v>61</v>
       </c>
-      <c r="F25" s="44" t="s">
+      <c r="F25" s="81" t="s">
         <v>36</v>
       </c>
-      <c r="G25" s="31"/>
-    </row>
-    <row r="26" ht="68.75" spans="3:7">
-      <c r="C26" s="8"/>
-      <c r="D26" s="15" t="s">
+      <c r="G25" s="62"/>
+    </row>
+    <row r="26" ht="68.75" spans="1:7">
+      <c r="A26" s="12"/>
+      <c r="B26" s="27"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="86" t="s">
         <v>62</v>
       </c>
-      <c r="E26" s="50" t="s">
+      <c r="F26" s="82" t="s">
+        <v>38</v>
+      </c>
+      <c r="G26" s="63"/>
+    </row>
+    <row r="27" ht="101.75" spans="1:7">
+      <c r="A27" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="F26" s="34"/>
-      <c r="G26" s="35" t="s">
+      <c r="B27" s="29" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="27" ht="68" spans="3:7">
-      <c r="C27" s="8"/>
-      <c r="D27" s="6" t="s">
+      <c r="C27" s="89" t="s">
+        <v>22</v>
+      </c>
+      <c r="D27" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="E27" s="41" t="s">
+      <c r="E27" s="90" t="s">
         <v>66</v>
       </c>
-      <c r="F27" s="51" t="s">
+      <c r="F27" s="43"/>
+      <c r="G27" s="57"/>
+    </row>
+    <row r="28" ht="152" spans="1:7">
+      <c r="A28" s="31" t="s">
         <v>67</v>
       </c>
-      <c r="G27" s="19"/>
-    </row>
-    <row r="28" ht="17" spans="3:7">
-      <c r="C28" s="8"/>
-      <c r="D28" s="9" t="s">
+      <c r="B28" s="32" t="s">
         <v>68</v>
       </c>
-      <c r="E28" s="43" t="s">
+      <c r="C28" s="91" t="s">
+        <v>22</v>
+      </c>
+      <c r="D28" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="F28" s="37"/>
-      <c r="G28" s="33" t="s">
+      <c r="E28" s="79" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="29" ht="84" spans="3:7">
-      <c r="C29" s="8"/>
-      <c r="D29" s="9" t="s">
+      <c r="F28" s="92" t="s">
+        <v>12</v>
+      </c>
+      <c r="G28" s="51"/>
+    </row>
+    <row r="29" ht="17" spans="1:7">
+      <c r="A29" s="34"/>
+      <c r="B29" s="35"/>
+      <c r="C29" s="36"/>
+      <c r="D29" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="E29" s="52" t="s">
+      <c r="E29" s="81" t="s">
         <v>72</v>
       </c>
-      <c r="F29" s="37"/>
-      <c r="G29" s="33"/>
-    </row>
-    <row r="30" ht="101.75" spans="3:7">
-      <c r="C30" s="8"/>
-      <c r="D30" s="12" t="s">
+      <c r="F29" s="65"/>
+      <c r="G29" s="62" t="s">
         <v>73</v>
       </c>
-      <c r="E30" s="44" t="s">
+    </row>
+    <row r="30" ht="84" spans="1:7">
+      <c r="A30" s="34"/>
+      <c r="B30" s="35"/>
+      <c r="C30" s="36"/>
+      <c r="D30" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="F30" s="39"/>
-      <c r="G30" s="24" t="s">
+      <c r="E30" s="93" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="31" ht="17" spans="3:7">
-      <c r="C31" s="8"/>
-      <c r="D31" s="6" t="s">
+      <c r="F30" s="65"/>
+      <c r="G30" s="62"/>
+    </row>
+    <row r="31" ht="84.75" spans="1:7">
+      <c r="A31" s="37"/>
+      <c r="B31" s="35"/>
+      <c r="C31" s="38"/>
+      <c r="D31" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="E31" s="41" t="s">
-        <v>26</v>
-      </c>
-      <c r="F31" s="42" t="s">
+      <c r="E31" s="82" t="s">
         <v>77</v>
       </c>
-      <c r="G31" s="19" t="s">
+      <c r="F31" s="67"/>
+      <c r="G31" s="54" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="32" ht="84.75" spans="3:7">
-      <c r="C32" s="8"/>
-      <c r="D32" s="12" t="s">
+    <row r="32" ht="17" spans="1:7">
+      <c r="A32" s="34" t="s">
         <v>79</v>
       </c>
-      <c r="E32" s="44" t="s">
-        <v>72</v>
-      </c>
-      <c r="F32" s="23"/>
-      <c r="G32" s="24"/>
+      <c r="B32" s="35"/>
+      <c r="C32" s="94" t="s">
+        <v>22</v>
+      </c>
+      <c r="D32" s="39" t="s">
+        <v>80</v>
+      </c>
+      <c r="E32" s="95" t="s">
+        <v>28</v>
+      </c>
+      <c r="F32" s="96" t="s">
+        <v>81</v>
+      </c>
+      <c r="G32" s="97" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="33" ht="84.75" spans="1:7">
+      <c r="A33" s="37"/>
+      <c r="B33" s="40"/>
+      <c r="C33" s="38"/>
+      <c r="D33" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="E33" s="82" t="s">
+        <v>75</v>
+      </c>
+      <c r="F33" s="49"/>
+      <c r="G33" s="54"/>
+    </row>
+    <row r="34" ht="185.75" spans="1:7">
+      <c r="A34" s="28" t="s">
+        <v>83</v>
+      </c>
+      <c r="B34" s="21" t="s">
+        <v>84</v>
+      </c>
+      <c r="C34" s="98" t="s">
+        <v>22</v>
+      </c>
+      <c r="D34" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="E34" s="90" t="s">
+        <v>86</v>
+      </c>
+      <c r="F34" s="43"/>
+      <c r="G34" s="57"/>
+    </row>
+    <row r="35" ht="17" spans="1:7">
+      <c r="A35" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="B35" s="24"/>
+      <c r="C35" s="78" t="s">
+        <v>22</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="E35" s="85" t="s">
+        <v>28</v>
+      </c>
+      <c r="F35" s="45"/>
+      <c r="G35" s="51"/>
+    </row>
+    <row r="36" s="1" customFormat="1" ht="51.75" spans="1:7">
+      <c r="A36" s="9"/>
+      <c r="B36" s="24"/>
+      <c r="C36" s="10"/>
+      <c r="D36" s="42" t="s">
+        <v>29</v>
+      </c>
+      <c r="E36" s="99" t="s">
+        <v>89</v>
+      </c>
+      <c r="F36" s="72"/>
+      <c r="G36" s="73"/>
+    </row>
+    <row r="37" ht="152" spans="1:7">
+      <c r="A37" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="B37" s="21" t="s">
+        <v>91</v>
+      </c>
+      <c r="C37" s="78" t="s">
+        <v>22</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="E37" s="79" t="s">
+        <v>93</v>
+      </c>
+      <c r="F37" s="80" t="s">
+        <v>12</v>
+      </c>
+      <c r="G37" s="51"/>
+    </row>
+    <row r="38" ht="28" customHeight="1" spans="1:7">
+      <c r="A38" s="9"/>
+      <c r="B38" s="24"/>
+      <c r="C38" s="10"/>
+      <c r="D38" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="E38" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="F38" s="52"/>
+      <c r="G38" s="74"/>
+    </row>
+    <row r="39" ht="71" customHeight="1" spans="1:7">
+      <c r="A39" s="12"/>
+      <c r="B39" s="24"/>
+      <c r="C39" s="13"/>
+      <c r="D39" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="E39" s="82" t="s">
+        <v>95</v>
+      </c>
+      <c r="F39" s="49"/>
+      <c r="G39" s="75"/>
+    </row>
+    <row r="40" ht="34" spans="1:7">
+      <c r="A40" s="34" t="s">
+        <v>96</v>
+      </c>
+      <c r="B40" s="24"/>
+      <c r="C40" s="100" t="s">
+        <v>22</v>
+      </c>
+      <c r="D40" s="39" t="s">
+        <v>97</v>
+      </c>
+      <c r="E40" s="95" t="s">
+        <v>28</v>
+      </c>
+      <c r="F40" s="96" t="s">
+        <v>98</v>
+      </c>
+      <c r="G40" s="101" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="41" ht="83" customHeight="1" spans="1:7">
+      <c r="A41" s="37"/>
+      <c r="B41" s="23"/>
+      <c r="C41" s="13"/>
+      <c r="D41" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="E41" s="82" t="s">
+        <v>95</v>
+      </c>
+      <c r="F41" s="49"/>
+      <c r="G41" s="63"/>
+    </row>
+    <row r="42" ht="152.75" spans="1:7">
+      <c r="A42" s="28" t="s">
+        <v>100</v>
+      </c>
+      <c r="B42" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="C42" s="90" t="s">
+        <v>102</v>
+      </c>
+      <c r="D42" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="E42" s="90" t="s">
+        <v>104</v>
+      </c>
+      <c r="F42" s="43"/>
+      <c r="G42" s="57"/>
+    </row>
+    <row r="43" ht="17.55" spans="1:7">
+      <c r="A43" s="36" t="s">
+        <v>105</v>
+      </c>
+      <c r="B43" s="36"/>
+      <c r="C43" s="36"/>
+      <c r="D43" s="36"/>
+      <c r="E43" s="36"/>
+      <c r="F43" s="36"/>
+      <c r="G43" s="36"/>
+    </row>
+    <row r="44" ht="58" customHeight="1" spans="1:7">
+      <c r="A44" s="31" t="s">
+        <v>106</v>
+      </c>
+      <c r="B44" s="44" t="s">
+        <v>107</v>
+      </c>
+      <c r="C44" s="79" t="s">
+        <v>108</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="E44" s="79" t="s">
+        <v>110</v>
+      </c>
+      <c r="F44" s="76"/>
+      <c r="G44" s="102" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="45" ht="100" customHeight="1" spans="1:7">
+      <c r="A45" s="37"/>
+      <c r="B45" s="46"/>
+      <c r="C45" s="47"/>
+      <c r="D45" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="E45" s="82" t="s">
+        <v>113</v>
+      </c>
+      <c r="F45" s="77"/>
+      <c r="G45" s="63"/>
+    </row>
+    <row r="46" ht="51" spans="1:7">
+      <c r="A46" s="31" t="s">
+        <v>114</v>
+      </c>
+      <c r="B46" s="44" t="s">
+        <v>115</v>
+      </c>
+      <c r="C46" s="80" t="s">
+        <v>108</v>
+      </c>
+      <c r="D46" s="44" t="s">
+        <v>116</v>
+      </c>
+      <c r="E46" s="79" t="s">
+        <v>117</v>
+      </c>
+      <c r="F46" s="79" t="s">
+        <v>118</v>
+      </c>
+      <c r="G46" s="51"/>
+    </row>
+    <row r="47" ht="51.75" spans="1:7">
+      <c r="A47" s="37"/>
+      <c r="B47" s="46"/>
+      <c r="C47" s="49"/>
+      <c r="D47" s="46"/>
+      <c r="E47" s="82" t="s">
+        <v>119</v>
+      </c>
+      <c r="F47" s="82" t="s">
+        <v>120</v>
+      </c>
+      <c r="G47" s="54"/>
     </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="63">
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A43:G43"/>
     <mergeCell ref="A2:A5"/>
-    <mergeCell ref="A6:A25"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A13:A15"/>
+    <mergeCell ref="A16:A19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A24:A26"/>
+    <mergeCell ref="A28:A31"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="A37:A39"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="A46:A47"/>
     <mergeCell ref="B2:B5"/>
-    <mergeCell ref="B6:B25"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B10:B19"/>
+    <mergeCell ref="B20:B23"/>
+    <mergeCell ref="B24:B26"/>
+    <mergeCell ref="B28:B33"/>
+    <mergeCell ref="B34:B36"/>
+    <mergeCell ref="B37:B41"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="B46:B47"/>
     <mergeCell ref="C2:C5"/>
-    <mergeCell ref="C6:C32"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="D17:D18"/>
-    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="C10:C12"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="C16:C19"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="C28:C31"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="C35:C36"/>
+    <mergeCell ref="C37:C39"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="C44:C45"/>
+    <mergeCell ref="C46:C47"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="D46:D47"/>
     <mergeCell ref="F2:F5"/>
-    <mergeCell ref="F27:F30"/>
-    <mergeCell ref="F31:F32"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="G9:G11"/>
-    <mergeCell ref="G12:G14"/>
-    <mergeCell ref="G15:G18"/>
-    <mergeCell ref="G19:G20"/>
-    <mergeCell ref="G21:G22"/>
-    <mergeCell ref="G23:G25"/>
-    <mergeCell ref="G28:G29"/>
-    <mergeCell ref="G31:G32"/>
+    <mergeCell ref="F28:F31"/>
+    <mergeCell ref="F32:F33"/>
+    <mergeCell ref="F37:F39"/>
+    <mergeCell ref="F40:F41"/>
+    <mergeCell ref="F44:F45"/>
+    <mergeCell ref="G10:G12"/>
+    <mergeCell ref="G13:G15"/>
+    <mergeCell ref="G16:G19"/>
+    <mergeCell ref="G20:G21"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="G24:G26"/>
+    <mergeCell ref="G29:G30"/>
+    <mergeCell ref="G32:G33"/>
+    <mergeCell ref="G40:G41"/>
+    <mergeCell ref="G44:G45"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/Doc_app/Test_case_ME_IOS.xlsx
+++ b/Doc_app/Test_case_ME_IOS.xlsx
@@ -4,10 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20360" windowHeight="16340"/>
+    <workbookView windowWidth="20360" windowHeight="16340" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="HOME_H" sheetId="1" r:id="rId1"/>
+    <sheet name="BASIC_EDIT_BE" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="127">
   <si>
     <t>ID</t>
   </si>
@@ -48,6 +49,9 @@
   </si>
   <si>
     <t>Note</t>
+  </si>
+  <si>
+    <t>kiểm thử UI</t>
   </si>
   <si>
     <t>UI_H</t>
@@ -465,6 +469,25 @@
   </si>
   <si>
     <t>- app "video eraser" đã có trong thiết bị</t>
+  </si>
+  <si>
+    <t>UI_BE_01</t>
+  </si>
+  <si>
+    <t>kiểm tra UI màn "Basic Edit" với Main panel</t>
+  </si>
+  <si>
+    <t>- màn "Basic Edit" 
+- ảnh input load thành công</t>
+  </si>
+  <si>
+    <t>1. kiểm tra UI</t>
+  </si>
+  <si>
+    <t>- hiển thị đúng, đầy đầy đủ các tool button trên main panel 
+- font-size, spacing, padding của các thành phần hiển thị đúng layout được thiết kế
+- font-color của text-label và icon có màu trắng khi máy ở dark mode và màu xám đậm (gần như đen) trên light mote, một số icon được giữ màu đỏ
+- không bị vỡ layout khi Large text mode được bật ở size lớn nhất</t>
   </si>
 </sst>
 </file>
@@ -863,6 +886,45 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="medium">
         <color auto="1"/>
       </left>
@@ -952,7 +1014,9 @@
       <left style="medium">
         <color auto="1"/>
       </left>
-      <right/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
       <top style="medium">
         <color auto="1"/>
       </top>
@@ -963,34 +1027,6 @@
     </border>
     <border>
       <left/>
-      <right/>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
       <right style="medium">
         <color auto="1"/>
       </right>
@@ -1028,19 +1064,6 @@
         <color auto="1"/>
       </right>
       <top/>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
@@ -1294,10 +1317,22 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1307,187 +1342,187 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1496,7 +1531,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1505,73 +1540,73 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
@@ -1586,23 +1621,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2137,840 +2175,914 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G47"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="7.546875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="11.5859375" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="3" customWidth="1"/>
-    <col min="4" max="4" width="29.5546875" style="3" customWidth="1"/>
-    <col min="5" max="5" width="40.1015625" style="3" customWidth="1"/>
-    <col min="6" max="6" width="13.015625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="12.109375" style="3" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="3"/>
+    <col min="1" max="1" width="7.546875" style="6" customWidth="1"/>
+    <col min="2" max="2" width="11.5859375" style="7" customWidth="1"/>
+    <col min="3" max="3" width="12.375" style="7" customWidth="1"/>
+    <col min="4" max="4" width="29.5546875" style="7" customWidth="1"/>
+    <col min="5" max="5" width="40.1015625" style="7" customWidth="1"/>
+    <col min="6" max="6" width="13.015625" style="7" customWidth="1"/>
+    <col min="7" max="7" width="12.109375" style="7" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1" spans="1:7">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="50" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" ht="17" spans="1:7">
-      <c r="A2" s="6" t="s">
+    <row r="2" ht="25" customHeight="1" spans="1:7">
+      <c r="A2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="54"/>
+    </row>
+    <row r="3" ht="17" spans="1:7">
+      <c r="A3" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="78" t="s">
+      <c r="B3" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="C3" s="82" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="79" t="s">
+      <c r="D3" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="80" t="s">
+      <c r="E3" s="83" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="51"/>
-    </row>
-    <row r="3" ht="135" customHeight="1" spans="1:7">
-      <c r="A3" s="9"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="11" t="s">
+      <c r="F3" s="84" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="81" t="s">
+      <c r="G3" s="55"/>
+    </row>
+    <row r="4" ht="135" customHeight="1" spans="1:7">
+      <c r="A4" s="13"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="52"/>
-      <c r="G3" s="53"/>
-    </row>
-    <row r="4" ht="34" spans="1:7">
-      <c r="A4" s="9"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="11" t="s">
+      <c r="E4" s="85" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="81" t="s">
+      <c r="F4" s="56"/>
+      <c r="G4" s="57"/>
+    </row>
+    <row r="5" ht="34" spans="1:7">
+      <c r="A5" s="13"/>
+      <c r="B5" s="14"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="52"/>
-      <c r="G4" s="53"/>
-    </row>
-    <row r="5" ht="101.75" spans="1:7">
-      <c r="A5" s="12"/>
-      <c r="B5" s="13"/>
-      <c r="C5" s="13"/>
-      <c r="D5" s="14" t="s">
+      <c r="E5" s="85" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="82" t="s">
+      <c r="F5" s="56"/>
+      <c r="G5" s="57"/>
+    </row>
+    <row r="6" ht="101.75" spans="1:7">
+      <c r="A6" s="16"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="49"/>
-      <c r="G5" s="54"/>
-    </row>
-    <row r="6" ht="17.55" spans="1:7">
-      <c r="A6" s="15" t="s">
+      <c r="E6" s="86" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="16"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="55"/>
-    </row>
-    <row r="7" ht="103" customHeight="1" spans="1:7">
-      <c r="A7" s="15" t="s">
+      <c r="F6" s="53"/>
+      <c r="G6" s="58"/>
+    </row>
+    <row r="7" ht="17.55" spans="1:7">
+      <c r="A7" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="20"/>
+      <c r="C7" s="21"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="20"/>
+      <c r="G7" s="59"/>
+    </row>
+    <row r="8" ht="103" customHeight="1" spans="1:7">
+      <c r="A8" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="83" t="s">
+      <c r="B8" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="19" t="s">
+      <c r="C8" s="87" t="s">
         <v>23</v>
       </c>
-      <c r="E7" s="84" t="s">
+      <c r="D8" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="F7" s="43"/>
-      <c r="G7" s="57"/>
-    </row>
-    <row r="8" ht="185" spans="1:7">
-      <c r="A8" s="20" t="s">
+      <c r="E8" s="88" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="F8" s="47"/>
+      <c r="G8" s="61"/>
+    </row>
+    <row r="9" ht="185" spans="1:7">
+      <c r="A9" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="78" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" s="8" t="s">
+      <c r="B9" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="E8" s="85" t="s">
+      <c r="C9" s="82" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="F8" s="45"/>
-      <c r="G8" s="51"/>
-    </row>
-    <row r="9" ht="51.75" spans="1:7">
-      <c r="A9" s="22"/>
-      <c r="B9" s="23"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="14" t="s">
+      <c r="E9" s="89" t="s">
         <v>29</v>
       </c>
-      <c r="E9" s="86" t="s">
+      <c r="F9" s="49"/>
+      <c r="G9" s="55"/>
+    </row>
+    <row r="10" ht="51.75" spans="1:7">
+      <c r="A10" s="26"/>
+      <c r="B10" s="27"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="F9" s="47"/>
-      <c r="G9" s="54"/>
-    </row>
-    <row r="10" ht="202" spans="1:7">
-      <c r="A10" s="6" t="s">
+      <c r="E10" s="90" t="s">
         <v>31</v>
       </c>
-      <c r="B10" s="21" t="s">
+      <c r="F10" s="51"/>
+      <c r="G10" s="58"/>
+    </row>
+    <row r="11" ht="202" spans="1:7">
+      <c r="A11" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="C10" s="78" t="s">
-        <v>22</v>
-      </c>
-      <c r="D10" s="8" t="s">
+      <c r="B11" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="E10" s="85" t="s">
-        <v>28</v>
-      </c>
-      <c r="F10" s="45"/>
-      <c r="G10" s="87" t="s">
+      <c r="C11" s="82" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" s="12" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="11" ht="101" spans="1:7">
-      <c r="A11" s="9"/>
-      <c r="B11" s="24"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="11" t="s">
+      <c r="E11" s="89" t="s">
         <v>29</v>
       </c>
-      <c r="E11" s="88" t="s">
+      <c r="F11" s="49"/>
+      <c r="G11" s="91" t="s">
         <v>35</v>
       </c>
-      <c r="F11" s="81" t="s">
+    </row>
+    <row r="12" ht="101" spans="1:7">
+      <c r="A12" s="13"/>
+      <c r="B12" s="28"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="E12" s="92" t="s">
         <v>36</v>
       </c>
-      <c r="G11" s="53"/>
-    </row>
-    <row r="12" ht="34.75" spans="1:7">
-      <c r="A12" s="12"/>
-      <c r="B12" s="24"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="86" t="s">
+      <c r="F12" s="85" t="s">
         <v>37</v>
       </c>
-      <c r="F12" s="82" t="s">
+      <c r="G12" s="57"/>
+    </row>
+    <row r="13" ht="34.75" spans="1:7">
+      <c r="A13" s="16"/>
+      <c r="B13" s="28"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="90" t="s">
         <v>38</v>
       </c>
-      <c r="G12" s="54"/>
-    </row>
-    <row r="13" ht="34" spans="1:7">
-      <c r="A13" s="6" t="s">
+      <c r="F13" s="86" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="24"/>
-      <c r="C13" s="78" t="s">
-        <v>22</v>
-      </c>
-      <c r="D13" s="8" t="s">
+      <c r="G13" s="58"/>
+    </row>
+    <row r="14" ht="34" spans="1:7">
+      <c r="A14" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="E13" s="85" t="s">
+      <c r="B14" s="28"/>
+      <c r="C14" s="82" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="F13" s="45"/>
-      <c r="G13" s="87" t="s">
+      <c r="E14" s="89" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="14" ht="68" spans="1:7">
-      <c r="A14" s="9"/>
-      <c r="B14" s="24"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="11" t="s">
+      <c r="F14" s="49"/>
+      <c r="G14" s="91" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="15" ht="68" spans="1:7">
+      <c r="A15" s="13"/>
+      <c r="B15" s="28"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="E15" s="92" t="s">
+        <v>44</v>
+      </c>
+      <c r="F15" s="85" t="s">
+        <v>37</v>
+      </c>
+      <c r="G15" s="57"/>
+    </row>
+    <row r="16" ht="34.75" spans="1:7">
+      <c r="A16" s="16"/>
+      <c r="B16" s="28"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="90" t="s">
+        <v>38</v>
+      </c>
+      <c r="F16" s="86" t="s">
+        <v>39</v>
+      </c>
+      <c r="G16" s="58"/>
+    </row>
+    <row r="17" ht="51" spans="1:7">
+      <c r="A17" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B17" s="28"/>
+      <c r="C17" s="82" t="s">
+        <v>23</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="E17" s="89" t="s">
+        <v>47</v>
+      </c>
+      <c r="F17" s="49"/>
+      <c r="G17" s="91" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" ht="17" spans="1:7">
+      <c r="A18" s="13"/>
+      <c r="B18" s="28"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="E18" s="92" t="s">
         <v>29</v>
       </c>
-      <c r="E14" s="88" t="s">
-        <v>43</v>
-      </c>
-      <c r="F14" s="81" t="s">
-        <v>36</v>
-      </c>
-      <c r="G14" s="53"/>
-    </row>
-    <row r="15" ht="34.75" spans="1:7">
-      <c r="A15" s="12"/>
-      <c r="B15" s="24"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="86" t="s">
+      <c r="G18" s="57"/>
+    </row>
+    <row r="19" ht="51" spans="1:7">
+      <c r="A19" s="13"/>
+      <c r="B19" s="28"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="E19" s="92" t="s">
+        <v>50</v>
+      </c>
+      <c r="F19" s="85" t="s">
         <v>37</v>
       </c>
-      <c r="F15" s="82" t="s">
-        <v>38</v>
-      </c>
-      <c r="G15" s="54"/>
-    </row>
-    <row r="16" ht="51" spans="1:7">
-      <c r="A16" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B16" s="24"/>
-      <c r="C16" s="78" t="s">
-        <v>22</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="E16" s="85" t="s">
-        <v>46</v>
-      </c>
-      <c r="F16" s="45"/>
-      <c r="G16" s="87" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="17" ht="17" spans="1:7">
-      <c r="A17" s="9"/>
-      <c r="B17" s="24"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="E17" s="88" t="s">
-        <v>28</v>
-      </c>
-      <c r="G17" s="53"/>
-    </row>
-    <row r="18" ht="51" spans="1:7">
-      <c r="A18" s="9"/>
-      <c r="B18" s="24"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="E18" s="88" t="s">
+      <c r="G19" s="57"/>
+    </row>
+    <row r="20" ht="34.75" spans="1:7">
+      <c r="A20" s="16"/>
+      <c r="B20" s="27"/>
+      <c r="C20" s="17"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="90" t="s">
+        <v>51</v>
+      </c>
+      <c r="F20" s="86" t="s">
+        <v>39</v>
+      </c>
+      <c r="G20" s="58"/>
+    </row>
+    <row r="21" ht="185" spans="1:7">
+      <c r="A21" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="B21" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="C21" s="82" t="s">
+        <v>23</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="E21" s="89" t="s">
+        <v>29</v>
+      </c>
+      <c r="F21" s="49"/>
+      <c r="G21" s="55"/>
+    </row>
+    <row r="22" ht="101.75" spans="1:7">
+      <c r="A22" s="16"/>
+      <c r="B22" s="30"/>
+      <c r="C22" s="17"/>
+      <c r="D22" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="E22" s="90" t="s">
+        <v>55</v>
+      </c>
+      <c r="F22" s="51"/>
+      <c r="G22" s="58"/>
+    </row>
+    <row r="23" ht="101" spans="1:7">
+      <c r="A23" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="B23" s="30"/>
+      <c r="C23" s="82" t="s">
+        <v>23</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="E23" s="89" t="s">
+        <v>29</v>
+      </c>
+      <c r="F23" s="49"/>
+      <c r="G23" s="55"/>
+    </row>
+    <row r="24" ht="101.75" spans="1:7">
+      <c r="A24" s="16"/>
+      <c r="B24" s="31"/>
+      <c r="C24" s="17"/>
+      <c r="D24" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="E24" s="90" t="s">
+        <v>58</v>
+      </c>
+      <c r="F24" s="51"/>
+      <c r="G24" s="58"/>
+    </row>
+    <row r="25" ht="185" spans="1:7">
+      <c r="A25" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="B25" s="29" t="s">
+        <v>60</v>
+      </c>
+      <c r="C25" s="82" t="s">
+        <v>23</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="E25" s="89" t="s">
+        <v>29</v>
+      </c>
+      <c r="F25" s="49"/>
+      <c r="G25" s="65"/>
+    </row>
+    <row r="26" ht="110" customHeight="1" spans="1:7">
+      <c r="A26" s="13"/>
+      <c r="B26" s="30"/>
+      <c r="C26" s="14"/>
+      <c r="D26" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="E26" s="92" t="s">
+        <v>62</v>
+      </c>
+      <c r="F26" s="85" t="s">
+        <v>37</v>
+      </c>
+      <c r="G26" s="66"/>
+    </row>
+    <row r="27" ht="68.75" spans="1:7">
+      <c r="A27" s="16"/>
+      <c r="B27" s="31"/>
+      <c r="C27" s="17"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="90" t="s">
+        <v>63</v>
+      </c>
+      <c r="F27" s="86" t="s">
+        <v>39</v>
+      </c>
+      <c r="G27" s="67"/>
+    </row>
+    <row r="28" ht="101.75" spans="1:7">
+      <c r="A28" s="32" t="s">
+        <v>64</v>
+      </c>
+      <c r="B28" s="33" t="s">
+        <v>65</v>
+      </c>
+      <c r="C28" s="93" t="s">
+        <v>23</v>
+      </c>
+      <c r="D28" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="E28" s="94" t="s">
+        <v>67</v>
+      </c>
+      <c r="F28" s="47"/>
+      <c r="G28" s="61"/>
+    </row>
+    <row r="29" ht="152" spans="1:7">
+      <c r="A29" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="B29" s="36" t="s">
+        <v>69</v>
+      </c>
+      <c r="C29" s="95" t="s">
+        <v>23</v>
+      </c>
+      <c r="D29" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="E29" s="83" t="s">
+        <v>71</v>
+      </c>
+      <c r="F29" s="96" t="s">
+        <v>13</v>
+      </c>
+      <c r="G29" s="55"/>
+    </row>
+    <row r="30" ht="17" spans="1:7">
+      <c r="A30" s="38"/>
+      <c r="B30" s="39"/>
+      <c r="C30" s="40"/>
+      <c r="D30" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="E30" s="85" t="s">
+        <v>73</v>
+      </c>
+      <c r="F30" s="69"/>
+      <c r="G30" s="66" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="31" ht="84" spans="1:7">
+      <c r="A31" s="38"/>
+      <c r="B31" s="39"/>
+      <c r="C31" s="40"/>
+      <c r="D31" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="E31" s="97" t="s">
+        <v>76</v>
+      </c>
+      <c r="F31" s="69"/>
+      <c r="G31" s="66"/>
+    </row>
+    <row r="32" ht="84.75" spans="1:7">
+      <c r="A32" s="41"/>
+      <c r="B32" s="39"/>
+      <c r="C32" s="42"/>
+      <c r="D32" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="E32" s="86" t="s">
+        <v>78</v>
+      </c>
+      <c r="F32" s="71"/>
+      <c r="G32" s="58" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="33" ht="17" spans="1:7">
+      <c r="A33" s="38" t="s">
+        <v>80</v>
+      </c>
+      <c r="B33" s="39"/>
+      <c r="C33" s="98" t="s">
+        <v>23</v>
+      </c>
+      <c r="D33" s="43" t="s">
+        <v>81</v>
+      </c>
+      <c r="E33" s="99" t="s">
+        <v>29</v>
+      </c>
+      <c r="F33" s="100" t="s">
+        <v>82</v>
+      </c>
+      <c r="G33" s="101" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="34" ht="84.75" spans="1:7">
+      <c r="A34" s="41"/>
+      <c r="B34" s="44"/>
+      <c r="C34" s="42"/>
+      <c r="D34" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="E34" s="86" t="s">
+        <v>76</v>
+      </c>
+      <c r="F34" s="53"/>
+      <c r="G34" s="58"/>
+    </row>
+    <row r="35" ht="185.75" spans="1:7">
+      <c r="A35" s="32" t="s">
+        <v>84</v>
+      </c>
+      <c r="B35" s="25" t="s">
+        <v>85</v>
+      </c>
+      <c r="C35" s="102" t="s">
+        <v>23</v>
+      </c>
+      <c r="D35" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="E35" s="94" t="s">
+        <v>87</v>
+      </c>
+      <c r="F35" s="47"/>
+      <c r="G35" s="61"/>
+    </row>
+    <row r="36" ht="17" spans="1:7">
+      <c r="A36" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="B36" s="28"/>
+      <c r="C36" s="82" t="s">
+        <v>23</v>
+      </c>
+      <c r="D36" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="E36" s="89" t="s">
+        <v>29</v>
+      </c>
+      <c r="F36" s="49"/>
+      <c r="G36" s="55"/>
+    </row>
+    <row r="37" s="5" customFormat="1" ht="51.75" spans="1:7">
+      <c r="A37" s="13"/>
+      <c r="B37" s="28"/>
+      <c r="C37" s="14"/>
+      <c r="D37" s="46" t="s">
+        <v>30</v>
+      </c>
+      <c r="E37" s="103" t="s">
+        <v>90</v>
+      </c>
+      <c r="F37" s="76"/>
+      <c r="G37" s="77"/>
+    </row>
+    <row r="38" ht="152" spans="1:7">
+      <c r="A38" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="B38" s="25" t="s">
+        <v>92</v>
+      </c>
+      <c r="C38" s="82" t="s">
+        <v>23</v>
+      </c>
+      <c r="D38" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="E38" s="83" t="s">
+        <v>94</v>
+      </c>
+      <c r="F38" s="84" t="s">
+        <v>13</v>
+      </c>
+      <c r="G38" s="55"/>
+    </row>
+    <row r="39" ht="28" customHeight="1" spans="1:7">
+      <c r="A39" s="13"/>
+      <c r="B39" s="28"/>
+      <c r="C39" s="14"/>
+      <c r="D39" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="E39" s="85" t="s">
+        <v>29</v>
+      </c>
+      <c r="F39" s="56"/>
+      <c r="G39" s="78"/>
+    </row>
+    <row r="40" ht="71" customHeight="1" spans="1:7">
+      <c r="A40" s="16"/>
+      <c r="B40" s="28"/>
+      <c r="C40" s="17"/>
+      <c r="D40" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="F18" s="81" t="s">
-        <v>36</v>
-      </c>
-      <c r="G18" s="53"/>
-    </row>
-    <row r="19" ht="34.75" spans="1:7">
-      <c r="A19" s="12"/>
-      <c r="B19" s="23"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="86" t="s">
-        <v>50</v>
-      </c>
-      <c r="F19" s="82" t="s">
-        <v>38</v>
-      </c>
-      <c r="G19" s="54"/>
-    </row>
-    <row r="20" ht="185" spans="1:7">
-      <c r="A20" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="B20" s="25" t="s">
-        <v>52</v>
-      </c>
-      <c r="C20" s="78" t="s">
-        <v>22</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="E20" s="85" t="s">
-        <v>28</v>
-      </c>
-      <c r="F20" s="45"/>
-      <c r="G20" s="51"/>
-    </row>
-    <row r="21" ht="101.75" spans="1:7">
-      <c r="A21" s="12"/>
-      <c r="B21" s="26"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="14" t="s">
+      <c r="E40" s="86" t="s">
+        <v>96</v>
+      </c>
+      <c r="F40" s="53"/>
+      <c r="G40" s="79"/>
+    </row>
+    <row r="41" ht="34" spans="1:7">
+      <c r="A41" s="38" t="s">
+        <v>97</v>
+      </c>
+      <c r="B41" s="28"/>
+      <c r="C41" s="104" t="s">
+        <v>23</v>
+      </c>
+      <c r="D41" s="43" t="s">
+        <v>98</v>
+      </c>
+      <c r="E41" s="99" t="s">
         <v>29</v>
       </c>
-      <c r="E21" s="86" t="s">
-        <v>54</v>
-      </c>
-      <c r="F21" s="47"/>
-      <c r="G21" s="54"/>
-    </row>
-    <row r="22" ht="101" spans="1:7">
-      <c r="A22" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B22" s="26"/>
-      <c r="C22" s="78" t="s">
-        <v>22</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="E22" s="85" t="s">
-        <v>28</v>
-      </c>
-      <c r="F22" s="45"/>
-      <c r="G22" s="51"/>
-    </row>
-    <row r="23" ht="101.75" spans="1:7">
-      <c r="A23" s="12"/>
-      <c r="B23" s="27"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="E23" s="86" t="s">
-        <v>57</v>
-      </c>
-      <c r="F23" s="47"/>
-      <c r="G23" s="54"/>
-    </row>
-    <row r="24" ht="185" spans="1:7">
-      <c r="A24" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="B24" s="25" t="s">
-        <v>59</v>
-      </c>
-      <c r="C24" s="78" t="s">
-        <v>22</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="E24" s="85" t="s">
-        <v>28</v>
-      </c>
-      <c r="F24" s="45"/>
-      <c r="G24" s="61"/>
-    </row>
-    <row r="25" ht="110" customHeight="1" spans="1:7">
-      <c r="A25" s="9"/>
-      <c r="B25" s="26"/>
-      <c r="C25" s="10"/>
-      <c r="D25" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="E25" s="88" t="s">
-        <v>61</v>
-      </c>
-      <c r="F25" s="81" t="s">
-        <v>36</v>
-      </c>
-      <c r="G25" s="62"/>
-    </row>
-    <row r="26" ht="68.75" spans="1:7">
-      <c r="A26" s="12"/>
-      <c r="B26" s="27"/>
-      <c r="C26" s="13"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="86" t="s">
-        <v>62</v>
-      </c>
-      <c r="F26" s="82" t="s">
-        <v>38</v>
-      </c>
-      <c r="G26" s="63"/>
-    </row>
-    <row r="27" ht="101.75" spans="1:7">
-      <c r="A27" s="28" t="s">
-        <v>63</v>
-      </c>
-      <c r="B27" s="29" t="s">
-        <v>64</v>
-      </c>
-      <c r="C27" s="89" t="s">
-        <v>22</v>
-      </c>
-      <c r="D27" s="19" t="s">
-        <v>65</v>
-      </c>
-      <c r="E27" s="90" t="s">
-        <v>66</v>
-      </c>
-      <c r="F27" s="43"/>
-      <c r="G27" s="57"/>
-    </row>
-    <row r="28" ht="152" spans="1:7">
-      <c r="A28" s="31" t="s">
-        <v>67</v>
-      </c>
-      <c r="B28" s="32" t="s">
-        <v>68</v>
-      </c>
-      <c r="C28" s="91" t="s">
-        <v>22</v>
-      </c>
-      <c r="D28" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="E28" s="79" t="s">
-        <v>70</v>
-      </c>
-      <c r="F28" s="92" t="s">
-        <v>12</v>
-      </c>
-      <c r="G28" s="51"/>
-    </row>
-    <row r="29" ht="17" spans="1:7">
-      <c r="A29" s="34"/>
-      <c r="B29" s="35"/>
-      <c r="C29" s="36"/>
-      <c r="D29" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="E29" s="81" t="s">
-        <v>72</v>
-      </c>
-      <c r="F29" s="65"/>
-      <c r="G29" s="62" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="30" ht="84" spans="1:7">
-      <c r="A30" s="34"/>
-      <c r="B30" s="35"/>
-      <c r="C30" s="36"/>
-      <c r="D30" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="E30" s="93" t="s">
-        <v>75</v>
-      </c>
-      <c r="F30" s="65"/>
-      <c r="G30" s="62"/>
-    </row>
-    <row r="31" ht="84.75" spans="1:7">
-      <c r="A31" s="37"/>
-      <c r="B31" s="35"/>
-      <c r="C31" s="38"/>
-      <c r="D31" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="E31" s="82" t="s">
-        <v>77</v>
-      </c>
-      <c r="F31" s="67"/>
-      <c r="G31" s="54" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="32" ht="17" spans="1:7">
-      <c r="A32" s="34" t="s">
-        <v>79</v>
-      </c>
-      <c r="B32" s="35"/>
-      <c r="C32" s="94" t="s">
-        <v>22</v>
-      </c>
-      <c r="D32" s="39" t="s">
-        <v>80</v>
-      </c>
-      <c r="E32" s="95" t="s">
-        <v>28</v>
-      </c>
-      <c r="F32" s="96" t="s">
-        <v>81</v>
-      </c>
-      <c r="G32" s="97" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="33" ht="84.75" spans="1:7">
-      <c r="A33" s="37"/>
-      <c r="B33" s="40"/>
-      <c r="C33" s="38"/>
-      <c r="D33" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="E33" s="82" t="s">
-        <v>75</v>
-      </c>
-      <c r="F33" s="49"/>
-      <c r="G33" s="54"/>
-    </row>
-    <row r="34" ht="185.75" spans="1:7">
-      <c r="A34" s="28" t="s">
-        <v>83</v>
-      </c>
-      <c r="B34" s="21" t="s">
-        <v>84</v>
-      </c>
-      <c r="C34" s="98" t="s">
-        <v>22</v>
-      </c>
-      <c r="D34" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="E34" s="90" t="s">
-        <v>86</v>
-      </c>
-      <c r="F34" s="43"/>
-      <c r="G34" s="57"/>
-    </row>
-    <row r="35" ht="17" spans="1:7">
-      <c r="A35" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="B35" s="24"/>
-      <c r="C35" s="78" t="s">
-        <v>22</v>
-      </c>
-      <c r="D35" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="E35" s="85" t="s">
-        <v>28</v>
-      </c>
-      <c r="F35" s="45"/>
-      <c r="G35" s="51"/>
-    </row>
-    <row r="36" s="1" customFormat="1" ht="51.75" spans="1:7">
-      <c r="A36" s="9"/>
-      <c r="B36" s="24"/>
-      <c r="C36" s="10"/>
-      <c r="D36" s="42" t="s">
-        <v>29</v>
-      </c>
-      <c r="E36" s="99" t="s">
-        <v>89</v>
-      </c>
-      <c r="F36" s="72"/>
-      <c r="G36" s="73"/>
-    </row>
-    <row r="37" ht="152" spans="1:7">
-      <c r="A37" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="B37" s="21" t="s">
-        <v>91</v>
-      </c>
-      <c r="C37" s="78" t="s">
-        <v>22</v>
-      </c>
-      <c r="D37" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="E37" s="79" t="s">
-        <v>93</v>
-      </c>
-      <c r="F37" s="80" t="s">
-        <v>12</v>
-      </c>
-      <c r="G37" s="51"/>
-    </row>
-    <row r="38" ht="28" customHeight="1" spans="1:7">
-      <c r="A38" s="9"/>
-      <c r="B38" s="24"/>
-      <c r="C38" s="10"/>
-      <c r="D38" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="E38" s="81" t="s">
-        <v>28</v>
-      </c>
-      <c r="F38" s="52"/>
-      <c r="G38" s="74"/>
-    </row>
-    <row r="39" ht="71" customHeight="1" spans="1:7">
-      <c r="A39" s="12"/>
-      <c r="B39" s="24"/>
-      <c r="C39" s="13"/>
-      <c r="D39" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="E39" s="82" t="s">
-        <v>95</v>
-      </c>
-      <c r="F39" s="49"/>
-      <c r="G39" s="75"/>
-    </row>
-    <row r="40" ht="34" spans="1:7">
-      <c r="A40" s="34" t="s">
+      <c r="F41" s="100" t="s">
+        <v>99</v>
+      </c>
+      <c r="G41" s="105" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42" ht="83" customHeight="1" spans="1:7">
+      <c r="A42" s="41"/>
+      <c r="B42" s="27"/>
+      <c r="C42" s="17"/>
+      <c r="D42" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="E42" s="86" t="s">
         <v>96</v>
       </c>
-      <c r="B40" s="24"/>
-      <c r="C40" s="100" t="s">
-        <v>22</v>
-      </c>
-      <c r="D40" s="39" t="s">
-        <v>97</v>
-      </c>
-      <c r="E40" s="95" t="s">
-        <v>28</v>
-      </c>
-      <c r="F40" s="96" t="s">
-        <v>98</v>
-      </c>
-      <c r="G40" s="101" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="41" ht="83" customHeight="1" spans="1:7">
-      <c r="A41" s="37"/>
-      <c r="B41" s="23"/>
-      <c r="C41" s="13"/>
-      <c r="D41" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="E41" s="82" t="s">
-        <v>95</v>
-      </c>
-      <c r="F41" s="49"/>
-      <c r="G41" s="63"/>
-    </row>
-    <row r="42" ht="152.75" spans="1:7">
-      <c r="A42" s="28" t="s">
-        <v>100</v>
-      </c>
-      <c r="B42" s="19" t="s">
+      <c r="F42" s="53"/>
+      <c r="G42" s="67"/>
+    </row>
+    <row r="43" ht="152.75" spans="1:7">
+      <c r="A43" s="32" t="s">
         <v>101</v>
       </c>
-      <c r="C42" s="90" t="s">
+      <c r="B43" s="23" t="s">
         <v>102</v>
       </c>
-      <c r="D42" s="19" t="s">
+      <c r="C43" s="94" t="s">
         <v>103</v>
       </c>
-      <c r="E42" s="90" t="s">
+      <c r="D43" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="F42" s="43"/>
-      <c r="G42" s="57"/>
-    </row>
-    <row r="43" ht="17.55" spans="1:7">
-      <c r="A43" s="36" t="s">
+      <c r="E43" s="94" t="s">
         <v>105</v>
       </c>
-      <c r="B43" s="36"/>
-      <c r="C43" s="36"/>
-      <c r="D43" s="36"/>
-      <c r="E43" s="36"/>
-      <c r="F43" s="36"/>
-      <c r="G43" s="36"/>
-    </row>
-    <row r="44" ht="58" customHeight="1" spans="1:7">
-      <c r="A44" s="31" t="s">
+      <c r="F43" s="47"/>
+      <c r="G43" s="61"/>
+    </row>
+    <row r="44" ht="17.55" spans="1:7">
+      <c r="A44" s="40" t="s">
         <v>106</v>
       </c>
-      <c r="B44" s="44" t="s">
+      <c r="B44" s="40"/>
+      <c r="C44" s="40"/>
+      <c r="D44" s="40"/>
+      <c r="E44" s="40"/>
+      <c r="F44" s="40"/>
+      <c r="G44" s="40"/>
+    </row>
+    <row r="45" ht="58" customHeight="1" spans="1:7">
+      <c r="A45" s="35" t="s">
         <v>107</v>
       </c>
-      <c r="C44" s="79" t="s">
+      <c r="B45" s="48" t="s">
         <v>108</v>
       </c>
-      <c r="D44" s="8" t="s">
+      <c r="C45" s="83" t="s">
         <v>109</v>
       </c>
-      <c r="E44" s="79" t="s">
+      <c r="D45" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="F44" s="76"/>
-      <c r="G44" s="102" t="s">
+      <c r="E45" s="83" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="45" ht="100" customHeight="1" spans="1:7">
-      <c r="A45" s="37"/>
-      <c r="B45" s="46"/>
-      <c r="C45" s="47"/>
-      <c r="D45" s="14" t="s">
+      <c r="F45" s="80"/>
+      <c r="G45" s="106" t="s">
         <v>112</v>
       </c>
-      <c r="E45" s="82" t="s">
+    </row>
+    <row r="46" ht="100" customHeight="1" spans="1:7">
+      <c r="A46" s="41"/>
+      <c r="B46" s="50"/>
+      <c r="C46" s="51"/>
+      <c r="D46" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="F45" s="77"/>
-      <c r="G45" s="63"/>
-    </row>
-    <row r="46" ht="51" spans="1:7">
-      <c r="A46" s="31" t="s">
+      <c r="E46" s="86" t="s">
         <v>114</v>
       </c>
-      <c r="B46" s="44" t="s">
+      <c r="F46" s="81"/>
+      <c r="G46" s="67"/>
+    </row>
+    <row r="47" ht="51" spans="1:7">
+      <c r="A47" s="35" t="s">
         <v>115</v>
       </c>
-      <c r="C46" s="80" t="s">
-        <v>108</v>
-      </c>
-      <c r="D46" s="44" t="s">
+      <c r="B47" s="48" t="s">
         <v>116</v>
       </c>
-      <c r="E46" s="79" t="s">
+      <c r="C47" s="84" t="s">
+        <v>109</v>
+      </c>
+      <c r="D47" s="48" t="s">
         <v>117</v>
       </c>
-      <c r="F46" s="79" t="s">
+      <c r="E47" s="83" t="s">
         <v>118</v>
       </c>
-      <c r="G46" s="51"/>
-    </row>
-    <row r="47" ht="51.75" spans="1:7">
-      <c r="A47" s="37"/>
-      <c r="B47" s="46"/>
-      <c r="C47" s="49"/>
-      <c r="D47" s="46"/>
-      <c r="E47" s="82" t="s">
+      <c r="F47" s="83" t="s">
         <v>119</v>
       </c>
-      <c r="F47" s="82" t="s">
+      <c r="G47" s="55"/>
+    </row>
+    <row r="48" ht="51.75" spans="1:7">
+      <c r="A48" s="41"/>
+      <c r="B48" s="50"/>
+      <c r="C48" s="53"/>
+      <c r="D48" s="50"/>
+      <c r="E48" s="86" t="s">
         <v>120</v>
       </c>
-      <c r="G47" s="54"/>
+      <c r="F48" s="86" t="s">
+        <v>121</v>
+      </c>
+      <c r="G48" s="58"/>
     </row>
   </sheetData>
-  <mergeCells count="63">
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A43:G43"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A10:A12"/>
-    <mergeCell ref="A13:A15"/>
-    <mergeCell ref="A16:A19"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="A24:A26"/>
-    <mergeCell ref="A28:A31"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="A37:A39"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="A46:A47"/>
-    <mergeCell ref="B2:B5"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="B10:B19"/>
-    <mergeCell ref="B20:B23"/>
-    <mergeCell ref="B24:B26"/>
-    <mergeCell ref="B28:B33"/>
-    <mergeCell ref="B34:B36"/>
-    <mergeCell ref="B37:B41"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="B46:B47"/>
-    <mergeCell ref="C2:C5"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="C10:C12"/>
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="C16:C19"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="C28:C31"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="C35:C36"/>
-    <mergeCell ref="C37:C39"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="C46:C47"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="D46:D47"/>
-    <mergeCell ref="F2:F5"/>
-    <mergeCell ref="F28:F31"/>
-    <mergeCell ref="F32:F33"/>
-    <mergeCell ref="F37:F39"/>
-    <mergeCell ref="F40:F41"/>
-    <mergeCell ref="F44:F45"/>
-    <mergeCell ref="G10:G12"/>
-    <mergeCell ref="G13:G15"/>
-    <mergeCell ref="G16:G19"/>
-    <mergeCell ref="G20:G21"/>
-    <mergeCell ref="G22:G23"/>
-    <mergeCell ref="G24:G26"/>
-    <mergeCell ref="G29:G30"/>
-    <mergeCell ref="G32:G33"/>
-    <mergeCell ref="G40:G41"/>
-    <mergeCell ref="G44:G45"/>
+  <mergeCells count="64">
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A44:G44"/>
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="A17:A20"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A29:A32"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A38:A40"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="A45:A46"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="B3:B6"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="B11:B20"/>
+    <mergeCell ref="B21:B24"/>
+    <mergeCell ref="B25:B27"/>
+    <mergeCell ref="B29:B34"/>
+    <mergeCell ref="B35:B37"/>
+    <mergeCell ref="B38:B42"/>
+    <mergeCell ref="B45:B46"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="C3:C6"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="C11:C13"/>
+    <mergeCell ref="C14:C16"/>
+    <mergeCell ref="C17:C20"/>
+    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="C25:C27"/>
+    <mergeCell ref="C29:C32"/>
+    <mergeCell ref="C33:C34"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="C38:C40"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="C45:C46"/>
+    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="D47:D48"/>
+    <mergeCell ref="F3:F6"/>
+    <mergeCell ref="F29:F32"/>
+    <mergeCell ref="F33:F34"/>
+    <mergeCell ref="F38:F40"/>
+    <mergeCell ref="F41:F42"/>
+    <mergeCell ref="F45:F46"/>
+    <mergeCell ref="G11:G13"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="G17:G20"/>
+    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="G23:G24"/>
+    <mergeCell ref="G25:G27"/>
+    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="G33:G34"/>
+    <mergeCell ref="G41:G42"/>
+    <mergeCell ref="G45:G46"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="1" outlineLevelCol="6"/>
+  <cols>
+    <col min="1" max="1" width="9.8984375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.015625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17.5703125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="23.3046875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="27.2109375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16.015625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="15.625" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1" spans="1:7">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" ht="219" spans="1:5">
+      <c r="A2" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C2" s="107" t="s">
+        <v>124</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E2" s="107" t="s">
+        <v>126</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/Doc_app/Test_case_ME_IOS.xlsx
+++ b/Doc_app/Test_case_ME_IOS.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20360" windowHeight="16340" activeTab="1"/>
+    <workbookView windowWidth="27320" windowHeight="9460" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="HOME_H" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="152">
   <si>
     <t>ID</t>
   </si>
@@ -481,13 +481,95 @@
 - ảnh input load thành công</t>
   </si>
   <si>
-    <t>1. kiểm tra UI</t>
+    <t>1. scoll ngang fearture view</t>
+  </si>
+  <si>
+    <t>- fearture view scoll mượt mà theo thao tác, không bị giật, khựng giữa chừng
+- button inset được neo ở vị trí đầu tiên của fearture view, không di chuyển khi có thao tác scroll</t>
+  </si>
+  <si>
+    <t>2. kiểm tra UI</t>
   </si>
   <si>
     <t>- hiển thị đúng, đầy đầy đủ các tool button trên main panel 
 - font-size, spacing, padding của các thành phần hiển thị đúng layout được thiết kế
 - font-color của text-label và icon có màu trắng khi máy ở dark mode và màu xám đậm (gần như đen) trên light mote, một số icon được giữ màu đỏ
 - không bị vỡ layout khi Large text mode được bật ở size lớn nhất</t>
+  </si>
+  <si>
+    <t>UI_BE_INS</t>
+  </si>
+  <si>
+    <t>kiểm tra UI dialog Add</t>
+  </si>
+  <si>
+    <t>- màn "Basic Edit"
+- ảnh input load thành công
+- main panel đang hiển thị</t>
+  </si>
+  <si>
+    <t>1. tap button "Insert"</t>
+  </si>
+  <si>
+    <t>- popup dialog "Add"</t>
+  </si>
+  <si>
+    <t>chức năng insert layer có ID: INS</t>
+  </si>
+  <si>
+    <t>2. scoll từ đầu tới cuối insert view</t>
+  </si>
+  <si>
+    <t>- hiển thị đầy đủ các button insert type: "Image", "Text", "AI Generate", "Graphics", "Sticker", "clipboard"(chức năng riêng của IOS)
+- hiển thị đầy đủ các mục chọn ảnh đơn của các nhóm: Image, Sticker, graphic, Text style
+- các thành phần UI hiển thị đúng icon, padding, màu sắc và không bị trùng lặp đúng theo thiết kế</t>
+  </si>
+  <si>
+    <t>3. scoll ngang lần lượt tất cả các insert layer scroll view</t>
+  </si>
+  <si>
+    <t>- hiển thị đầy đủ và load thành công tất cả các preview của mọi button (không spin/load vô hạn)</t>
+  </si>
+  <si>
+    <t>F_BE_INS__IMG_01</t>
+  </si>
+  <si>
+    <t>kiểm tra khả năng insert Image layer mới</t>
+  </si>
+  <si>
+    <t>- màn "Basic Edit"
+- dialog "Add" đang hiển thị</t>
+  </si>
+  <si>
+    <t>1. tap button "Image"</t>
+  </si>
+  <si>
+    <t>- chuyển sang sheet "Add Image"</t>
+  </si>
+  <si>
+    <t>- về màn Basic Edit 
+- insert Image layer mới là ảnh vừa chọn thành công</t>
+  </si>
+  <si>
+    <t>F_BE_INS_IMG_02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- màn "Basic Edit" </t>
+  </si>
+  <si>
+    <t>2. tap button "Camera"</t>
+  </si>
+  <si>
+    <t>- chuyển sang giao diện camera của OS</t>
+  </si>
+  <si>
+    <t>3. chụp ảnh</t>
+  </si>
+  <si>
+    <t>- ảnh được chụp thành công</t>
+  </si>
+  <si>
+    <t>4. xác nhận sử dụng ảnh</t>
   </si>
 </sst>
 </file>
@@ -1317,31 +1399,31 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1360,9 +1442,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1390,33 +1469,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1438,57 +1499,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1498,81 +1523,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1600,47 +1556,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" quotePrefix="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2178,36 +2104,36 @@
   <dimension ref="A1:G48"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="7.546875" style="6" customWidth="1"/>
-    <col min="2" max="2" width="11.5859375" style="7" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="7" customWidth="1"/>
-    <col min="4" max="4" width="29.5546875" style="7" customWidth="1"/>
-    <col min="5" max="5" width="40.1015625" style="7" customWidth="1"/>
-    <col min="6" max="6" width="13.015625" style="7" customWidth="1"/>
-    <col min="7" max="7" width="12.109375" style="7" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="7"/>
+    <col min="1" max="1" width="7.546875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="11.5859375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="12.375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="29.5546875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="40.1015625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="13.015625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="12.109375" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1" spans="1:7">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
     </row>
@@ -2220,7 +2146,7 @@
       <c r="D2" s="9"/>
       <c r="E2" s="9"/>
       <c r="F2" s="9"/>
-      <c r="G2" s="54"/>
+      <c r="G2" s="36"/>
     </row>
     <row r="3" ht="17" spans="1:7">
       <c r="A3" s="10" t="s">
@@ -2229,729 +2155,716 @@
       <c r="B3" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="82" t="s">
+      <c r="C3" s="42" t="s">
         <v>10</v>
       </c>
       <c r="D3" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="83" t="s">
+      <c r="E3" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="84" t="s">
+      <c r="F3" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="55"/>
+      <c r="G3" s="37"/>
     </row>
     <row r="4" ht="135" customHeight="1" spans="1:7">
       <c r="A4" s="13"/>
-      <c r="B4" s="14"/>
-      <c r="C4" s="14"/>
-      <c r="D4" s="15" t="s">
+      <c r="D4" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="85" t="s">
+      <c r="E4" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="56"/>
-      <c r="G4" s="57"/>
+      <c r="G4" s="38"/>
     </row>
     <row r="5" ht="34" spans="1:7">
       <c r="A5" s="13"/>
-      <c r="B5" s="14"/>
-      <c r="C5" s="14"/>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="85" t="s">
+      <c r="E5" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="F5" s="56"/>
-      <c r="G5" s="57"/>
+      <c r="G5" s="38"/>
     </row>
     <row r="6" ht="101.75" spans="1:7">
-      <c r="A6" s="16"/>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="18" t="s">
+      <c r="A6" s="15"/>
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="86" t="s">
+      <c r="E6" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="F6" s="53"/>
-      <c r="G6" s="58"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="39"/>
     </row>
     <row r="7" ht="17.55" spans="1:7">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="20"/>
-      <c r="C7" s="21"/>
-      <c r="D7" s="20"/>
-      <c r="E7" s="20"/>
-      <c r="F7" s="20"/>
-      <c r="G7" s="59"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="40"/>
     </row>
     <row r="8" ht="103" customHeight="1" spans="1:7">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="87" t="s">
+      <c r="C8" s="45" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="23" t="s">
+      <c r="D8" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="E8" s="88" t="s">
+      <c r="E8" s="46" t="s">
         <v>25</v>
       </c>
-      <c r="F8" s="47"/>
-      <c r="G8" s="61"/>
+      <c r="F8" s="27"/>
+      <c r="G8" s="41"/>
     </row>
     <row r="9" ht="185" spans="1:7">
-      <c r="A9" s="24" t="s">
+      <c r="A9" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="25" t="s">
+      <c r="B9" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="82" t="s">
+      <c r="C9" s="42" t="s">
         <v>23</v>
       </c>
       <c r="D9" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="E9" s="89" t="s">
+      <c r="E9" s="47" t="s">
         <v>29</v>
       </c>
-      <c r="F9" s="49"/>
-      <c r="G9" s="55"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="37"/>
     </row>
     <row r="10" ht="51.75" spans="1:7">
-      <c r="A10" s="26"/>
-      <c r="B10" s="27"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="18" t="s">
+      <c r="A10" s="15"/>
+      <c r="B10" s="24"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="E10" s="90" t="s">
+      <c r="E10" s="48" t="s">
         <v>31</v>
       </c>
-      <c r="F10" s="51"/>
-      <c r="G10" s="58"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="39"/>
     </row>
     <row r="11" ht="202" spans="1:7">
       <c r="A11" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="B11" s="25" t="s">
+      <c r="B11" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="82" t="s">
+      <c r="C11" s="42" t="s">
         <v>23</v>
       </c>
       <c r="D11" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="E11" s="89" t="s">
+      <c r="E11" s="47" t="s">
         <v>29</v>
       </c>
-      <c r="F11" s="49"/>
-      <c r="G11" s="91" t="s">
+      <c r="F11" s="11"/>
+      <c r="G11" s="49" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="12" ht="101" spans="1:7">
       <c r="A12" s="13"/>
-      <c r="B12" s="28"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="15" t="s">
+      <c r="B12" s="25"/>
+      <c r="D12" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="E12" s="92" t="s">
+      <c r="E12" s="50" t="s">
         <v>36</v>
       </c>
-      <c r="F12" s="85" t="s">
+      <c r="F12" s="43" t="s">
         <v>37</v>
       </c>
-      <c r="G12" s="57"/>
+      <c r="G12" s="38"/>
     </row>
     <row r="13" ht="34.75" spans="1:7">
-      <c r="A13" s="16"/>
-      <c r="B13" s="28"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="90" t="s">
+      <c r="A13" s="15"/>
+      <c r="B13" s="25"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="48" t="s">
         <v>38</v>
       </c>
-      <c r="F13" s="86" t="s">
+      <c r="F13" s="44" t="s">
         <v>39</v>
       </c>
-      <c r="G13" s="58"/>
+      <c r="G13" s="39"/>
     </row>
     <row r="14" ht="34" spans="1:7">
       <c r="A14" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B14" s="28"/>
-      <c r="C14" s="82" t="s">
+      <c r="B14" s="25"/>
+      <c r="C14" s="42" t="s">
         <v>23</v>
       </c>
       <c r="D14" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="E14" s="89" t="s">
+      <c r="E14" s="47" t="s">
         <v>42</v>
       </c>
-      <c r="F14" s="49"/>
-      <c r="G14" s="91" t="s">
+      <c r="F14" s="11"/>
+      <c r="G14" s="49" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="15" ht="68" spans="1:7">
       <c r="A15" s="13"/>
-      <c r="B15" s="28"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="15" t="s">
+      <c r="B15" s="25"/>
+      <c r="D15" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="E15" s="92" t="s">
+      <c r="E15" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="F15" s="85" t="s">
+      <c r="F15" s="43" t="s">
         <v>37</v>
       </c>
-      <c r="G15" s="57"/>
+      <c r="G15" s="38"/>
     </row>
     <row r="16" ht="34.75" spans="1:7">
-      <c r="A16" s="16"/>
-      <c r="B16" s="28"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="90" t="s">
+      <c r="A16" s="15"/>
+      <c r="B16" s="25"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="48" t="s">
         <v>38</v>
       </c>
-      <c r="F16" s="86" t="s">
+      <c r="F16" s="44" t="s">
         <v>39</v>
       </c>
-      <c r="G16" s="58"/>
+      <c r="G16" s="39"/>
     </row>
     <row r="17" ht="51" spans="1:7">
       <c r="A17" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="B17" s="28"/>
-      <c r="C17" s="82" t="s">
+      <c r="B17" s="25"/>
+      <c r="C17" s="42" t="s">
         <v>23</v>
       </c>
       <c r="D17" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="E17" s="89" t="s">
+      <c r="E17" s="47" t="s">
         <v>47</v>
       </c>
-      <c r="F17" s="49"/>
-      <c r="G17" s="91" t="s">
+      <c r="F17" s="11"/>
+      <c r="G17" s="49" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="18" ht="17" spans="1:7">
       <c r="A18" s="13"/>
-      <c r="B18" s="28"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="15" t="s">
+      <c r="B18" s="25"/>
+      <c r="D18" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="E18" s="92" t="s">
+      <c r="E18" s="50" t="s">
         <v>29</v>
       </c>
-      <c r="G18" s="57"/>
+      <c r="G18" s="38"/>
     </row>
     <row r="19" ht="51" spans="1:7">
       <c r="A19" s="13"/>
-      <c r="B19" s="28"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="15" t="s">
+      <c r="B19" s="25"/>
+      <c r="D19" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="E19" s="92" t="s">
+      <c r="E19" s="50" t="s">
         <v>50</v>
       </c>
-      <c r="F19" s="85" t="s">
+      <c r="F19" s="43" t="s">
         <v>37</v>
       </c>
-      <c r="G19" s="57"/>
+      <c r="G19" s="38"/>
     </row>
     <row r="20" ht="34.75" spans="1:7">
-      <c r="A20" s="16"/>
-      <c r="B20" s="27"/>
-      <c r="C20" s="17"/>
-      <c r="D20" s="18"/>
-      <c r="E20" s="90" t="s">
+      <c r="A20" s="15"/>
+      <c r="B20" s="24"/>
+      <c r="C20" s="16"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="48" t="s">
         <v>51</v>
       </c>
-      <c r="F20" s="86" t="s">
+      <c r="F20" s="44" t="s">
         <v>39</v>
       </c>
-      <c r="G20" s="58"/>
+      <c r="G20" s="39"/>
     </row>
     <row r="21" ht="185" spans="1:7">
       <c r="A21" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="B21" s="29" t="s">
+      <c r="B21" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="C21" s="82" t="s">
+      <c r="C21" s="42" t="s">
         <v>23</v>
       </c>
       <c r="D21" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="E21" s="89" t="s">
+      <c r="E21" s="47" t="s">
         <v>29</v>
       </c>
-      <c r="F21" s="49"/>
-      <c r="G21" s="55"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="37"/>
     </row>
     <row r="22" ht="101.75" spans="1:7">
-      <c r="A22" s="16"/>
-      <c r="B22" s="30"/>
-      <c r="C22" s="17"/>
-      <c r="D22" s="18" t="s">
+      <c r="A22" s="15"/>
+      <c r="B22" s="14"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="E22" s="90" t="s">
+      <c r="E22" s="48" t="s">
         <v>55</v>
       </c>
-      <c r="F22" s="51"/>
-      <c r="G22" s="58"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="39"/>
     </row>
     <row r="23" ht="101" spans="1:7">
       <c r="A23" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="B23" s="30"/>
-      <c r="C23" s="82" t="s">
+      <c r="B23" s="14"/>
+      <c r="C23" s="42" t="s">
         <v>23</v>
       </c>
       <c r="D23" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="E23" s="89" t="s">
+      <c r="E23" s="47" t="s">
         <v>29</v>
       </c>
-      <c r="F23" s="49"/>
-      <c r="G23" s="55"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="37"/>
     </row>
     <row r="24" ht="101.75" spans="1:7">
-      <c r="A24" s="16"/>
-      <c r="B24" s="31"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="18" t="s">
+      <c r="A24" s="15"/>
+      <c r="B24" s="17"/>
+      <c r="C24" s="16"/>
+      <c r="D24" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="E24" s="90" t="s">
+      <c r="E24" s="48" t="s">
         <v>58</v>
       </c>
-      <c r="F24" s="51"/>
-      <c r="G24" s="58"/>
+      <c r="F24" s="16"/>
+      <c r="G24" s="39"/>
     </row>
     <row r="25" ht="185" spans="1:7">
       <c r="A25" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="B25" s="29" t="s">
+      <c r="B25" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="C25" s="82" t="s">
+      <c r="C25" s="42" t="s">
         <v>23</v>
       </c>
       <c r="D25" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="E25" s="89" t="s">
+      <c r="E25" s="47" t="s">
         <v>29</v>
       </c>
-      <c r="F25" s="49"/>
-      <c r="G25" s="65"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="37"/>
     </row>
     <row r="26" ht="110" customHeight="1" spans="1:7">
       <c r="A26" s="13"/>
-      <c r="B26" s="30"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="15" t="s">
+      <c r="B26" s="14"/>
+      <c r="D26" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="E26" s="92" t="s">
+      <c r="E26" s="50" t="s">
         <v>62</v>
       </c>
-      <c r="F26" s="85" t="s">
+      <c r="F26" s="43" t="s">
         <v>37</v>
       </c>
-      <c r="G26" s="66"/>
+      <c r="G26" s="38"/>
     </row>
     <row r="27" ht="68.75" spans="1:7">
-      <c r="A27" s="16"/>
-      <c r="B27" s="31"/>
-      <c r="C27" s="17"/>
-      <c r="D27" s="18"/>
-      <c r="E27" s="90" t="s">
+      <c r="A27" s="15"/>
+      <c r="B27" s="17"/>
+      <c r="C27" s="16"/>
+      <c r="D27" s="17"/>
+      <c r="E27" s="48" t="s">
         <v>63</v>
       </c>
-      <c r="F27" s="86" t="s">
+      <c r="F27" s="44" t="s">
         <v>39</v>
       </c>
-      <c r="G27" s="67"/>
+      <c r="G27" s="39"/>
     </row>
     <row r="28" ht="101.75" spans="1:7">
-      <c r="A28" s="32" t="s">
+      <c r="A28" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="B28" s="33" t="s">
+      <c r="B28" s="26" t="s">
         <v>65</v>
       </c>
-      <c r="C28" s="93" t="s">
+      <c r="C28" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="D28" s="23" t="s">
+      <c r="D28" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="E28" s="94" t="s">
+      <c r="E28" s="51" t="s">
         <v>67</v>
       </c>
-      <c r="F28" s="47"/>
-      <c r="G28" s="61"/>
+      <c r="F28" s="27"/>
+      <c r="G28" s="41"/>
     </row>
     <row r="29" ht="152" spans="1:7">
-      <c r="A29" s="35" t="s">
+      <c r="A29" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="B29" s="36" t="s">
+      <c r="B29" s="29" t="s">
         <v>69</v>
       </c>
-      <c r="C29" s="95" t="s">
+      <c r="C29" s="52" t="s">
         <v>23</v>
       </c>
       <c r="D29" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="E29" s="83" t="s">
+      <c r="E29" s="42" t="s">
         <v>71</v>
       </c>
-      <c r="F29" s="96" t="s">
+      <c r="F29" s="52" t="s">
         <v>13</v>
       </c>
-      <c r="G29" s="55"/>
+      <c r="G29" s="37"/>
     </row>
     <row r="30" ht="17" spans="1:7">
-      <c r="A30" s="38"/>
-      <c r="B30" s="39"/>
-      <c r="C30" s="40"/>
-      <c r="D30" s="15" t="s">
+      <c r="A30" s="31"/>
+      <c r="B30" s="32"/>
+      <c r="C30" s="5"/>
+      <c r="D30" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="E30" s="85" t="s">
+      <c r="E30" s="43" t="s">
         <v>73</v>
       </c>
-      <c r="F30" s="69"/>
-      <c r="G30" s="66" t="s">
+      <c r="F30" s="5"/>
+      <c r="G30" s="38" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="31" ht="84" spans="1:7">
-      <c r="A31" s="38"/>
-      <c r="B31" s="39"/>
-      <c r="C31" s="40"/>
-      <c r="D31" s="15" t="s">
+      <c r="A31" s="31"/>
+      <c r="B31" s="32"/>
+      <c r="C31" s="5"/>
+      <c r="D31" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="E31" s="97" t="s">
+      <c r="E31" s="53" t="s">
         <v>76</v>
       </c>
-      <c r="F31" s="69"/>
-      <c r="G31" s="66"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="38"/>
     </row>
     <row r="32" ht="84.75" spans="1:7">
-      <c r="A32" s="41"/>
-      <c r="B32" s="39"/>
-      <c r="C32" s="42"/>
-      <c r="D32" s="18" t="s">
+      <c r="A32" s="33"/>
+      <c r="B32" s="32"/>
+      <c r="C32" s="34"/>
+      <c r="D32" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="E32" s="86" t="s">
+      <c r="E32" s="44" t="s">
         <v>78</v>
       </c>
-      <c r="F32" s="71"/>
-      <c r="G32" s="58" t="s">
+      <c r="F32" s="34"/>
+      <c r="G32" s="39" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="33" ht="17" spans="1:7">
-      <c r="A33" s="38" t="s">
+      <c r="A33" s="31" t="s">
         <v>80</v>
       </c>
-      <c r="B33" s="39"/>
-      <c r="C33" s="98" t="s">
+      <c r="B33" s="32"/>
+      <c r="C33" s="54" t="s">
         <v>23</v>
       </c>
-      <c r="D33" s="43" t="s">
+      <c r="D33" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="E33" s="99" t="s">
+      <c r="E33" s="53" t="s">
         <v>29</v>
       </c>
-      <c r="F33" s="100" t="s">
+      <c r="F33" s="53" t="s">
         <v>82</v>
       </c>
-      <c r="G33" s="101" t="s">
+      <c r="G33" s="55" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="34" ht="84.75" spans="1:7">
-      <c r="A34" s="41"/>
-      <c r="B34" s="44"/>
-      <c r="C34" s="42"/>
-      <c r="D34" s="18" t="s">
+      <c r="A34" s="33"/>
+      <c r="B34" s="35"/>
+      <c r="C34" s="34"/>
+      <c r="D34" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="E34" s="86" t="s">
+      <c r="E34" s="44" t="s">
         <v>76</v>
       </c>
-      <c r="F34" s="53"/>
-      <c r="G34" s="58"/>
+      <c r="F34" s="16"/>
+      <c r="G34" s="39"/>
     </row>
     <row r="35" ht="185.75" spans="1:7">
-      <c r="A35" s="32" t="s">
+      <c r="A35" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="B35" s="25" t="s">
+      <c r="B35" s="23" t="s">
         <v>85</v>
       </c>
-      <c r="C35" s="102" t="s">
+      <c r="C35" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="D35" s="23" t="s">
+      <c r="D35" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="E35" s="94" t="s">
+      <c r="E35" s="51" t="s">
         <v>87</v>
       </c>
-      <c r="F35" s="47"/>
-      <c r="G35" s="61"/>
+      <c r="F35" s="27"/>
+      <c r="G35" s="41"/>
     </row>
     <row r="36" ht="17" spans="1:7">
       <c r="A36" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="B36" s="28"/>
-      <c r="C36" s="82" t="s">
+      <c r="B36" s="25"/>
+      <c r="C36" s="42" t="s">
         <v>23</v>
       </c>
       <c r="D36" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="E36" s="89" t="s">
+      <c r="E36" s="47" t="s">
         <v>29</v>
       </c>
-      <c r="F36" s="49"/>
-      <c r="G36" s="55"/>
-    </row>
-    <row r="37" s="5" customFormat="1" ht="51.75" spans="1:7">
+      <c r="F36" s="11"/>
+      <c r="G36" s="37"/>
+    </row>
+    <row r="37" s="7" customFormat="1" ht="51.75" spans="1:7">
       <c r="A37" s="13"/>
-      <c r="B37" s="28"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="46" t="s">
+      <c r="B37" s="25"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="E37" s="103" t="s">
+      <c r="E37" s="48" t="s">
         <v>90</v>
       </c>
-      <c r="F37" s="76"/>
-      <c r="G37" s="77"/>
+      <c r="F37" s="16"/>
+      <c r="G37" s="39"/>
     </row>
     <row r="38" ht="152" spans="1:7">
       <c r="A38" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="B38" s="25" t="s">
+      <c r="B38" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="C38" s="82" t="s">
+      <c r="C38" s="42" t="s">
         <v>23</v>
       </c>
       <c r="D38" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="E38" s="83" t="s">
+      <c r="E38" s="42" t="s">
         <v>94</v>
       </c>
-      <c r="F38" s="84" t="s">
+      <c r="F38" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="G38" s="55"/>
+      <c r="G38" s="37"/>
     </row>
     <row r="39" ht="28" customHeight="1" spans="1:7">
       <c r="A39" s="13"/>
-      <c r="B39" s="28"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="15" t="s">
+      <c r="B39" s="25"/>
+      <c r="D39" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="E39" s="85" t="s">
+      <c r="E39" s="43" t="s">
         <v>29</v>
       </c>
-      <c r="F39" s="56"/>
-      <c r="G39" s="78"/>
+      <c r="G39" s="38"/>
     </row>
     <row r="40" ht="71" customHeight="1" spans="1:7">
-      <c r="A40" s="16"/>
-      <c r="B40" s="28"/>
-      <c r="C40" s="17"/>
-      <c r="D40" s="18" t="s">
+      <c r="A40" s="15"/>
+      <c r="B40" s="25"/>
+      <c r="C40" s="16"/>
+      <c r="D40" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="E40" s="86" t="s">
+      <c r="E40" s="44" t="s">
         <v>96</v>
       </c>
-      <c r="F40" s="53"/>
-      <c r="G40" s="79"/>
+      <c r="F40" s="16"/>
+      <c r="G40" s="39"/>
     </row>
     <row r="41" ht="34" spans="1:7">
-      <c r="A41" s="38" t="s">
+      <c r="A41" s="31" t="s">
         <v>97</v>
       </c>
-      <c r="B41" s="28"/>
-      <c r="C41" s="104" t="s">
+      <c r="B41" s="25"/>
+      <c r="C41" s="43" t="s">
         <v>23</v>
       </c>
-      <c r="D41" s="43" t="s">
+      <c r="D41" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="E41" s="99" t="s">
+      <c r="E41" s="53" t="s">
         <v>29</v>
       </c>
-      <c r="F41" s="100" t="s">
+      <c r="F41" s="53" t="s">
         <v>99</v>
       </c>
-      <c r="G41" s="105" t="s">
+      <c r="G41" s="55" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="42" ht="83" customHeight="1" spans="1:7">
-      <c r="A42" s="41"/>
-      <c r="B42" s="27"/>
-      <c r="C42" s="17"/>
-      <c r="D42" s="18" t="s">
+      <c r="A42" s="33"/>
+      <c r="B42" s="24"/>
+      <c r="C42" s="16"/>
+      <c r="D42" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="E42" s="86" t="s">
+      <c r="E42" s="44" t="s">
         <v>96</v>
       </c>
-      <c r="F42" s="53"/>
-      <c r="G42" s="67"/>
+      <c r="F42" s="16"/>
+      <c r="G42" s="39"/>
     </row>
     <row r="43" ht="152.75" spans="1:7">
-      <c r="A43" s="32" t="s">
+      <c r="A43" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="B43" s="23" t="s">
+      <c r="B43" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="C43" s="94" t="s">
+      <c r="C43" s="51" t="s">
         <v>103</v>
       </c>
-      <c r="D43" s="23" t="s">
+      <c r="D43" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="E43" s="94" t="s">
+      <c r="E43" s="51" t="s">
         <v>105</v>
       </c>
-      <c r="F43" s="47"/>
-      <c r="G43" s="61"/>
+      <c r="F43" s="27"/>
+      <c r="G43" s="41"/>
     </row>
     <row r="44" ht="17.55" spans="1:7">
-      <c r="A44" s="40" t="s">
+      <c r="A44" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="B44" s="40"/>
-      <c r="C44" s="40"/>
-      <c r="D44" s="40"/>
-      <c r="E44" s="40"/>
-      <c r="F44" s="40"/>
-      <c r="G44" s="40"/>
+      <c r="B44" s="5"/>
+      <c r="C44" s="5"/>
+      <c r="D44" s="5"/>
+      <c r="E44" s="5"/>
+      <c r="F44" s="5"/>
+      <c r="G44" s="5"/>
     </row>
     <row r="45" ht="58" customHeight="1" spans="1:7">
-      <c r="A45" s="35" t="s">
+      <c r="A45" s="28" t="s">
         <v>107</v>
       </c>
-      <c r="B45" s="48" t="s">
+      <c r="B45" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="C45" s="83" t="s">
+      <c r="C45" s="42" t="s">
         <v>109</v>
       </c>
       <c r="D45" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="E45" s="83" t="s">
+      <c r="E45" s="42" t="s">
         <v>111</v>
       </c>
-      <c r="F45" s="80"/>
-      <c r="G45" s="106" t="s">
+      <c r="F45" s="11"/>
+      <c r="G45" s="49" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="46" ht="100" customHeight="1" spans="1:7">
-      <c r="A46" s="41"/>
-      <c r="B46" s="50"/>
-      <c r="C46" s="51"/>
-      <c r="D46" s="18" t="s">
+      <c r="A46" s="33"/>
+      <c r="B46" s="17"/>
+      <c r="C46" s="16"/>
+      <c r="D46" s="17" t="s">
         <v>113</v>
       </c>
-      <c r="E46" s="86" t="s">
+      <c r="E46" s="44" t="s">
         <v>114</v>
       </c>
-      <c r="F46" s="81"/>
-      <c r="G46" s="67"/>
+      <c r="F46" s="16"/>
+      <c r="G46" s="39"/>
     </row>
     <row r="47" ht="51" spans="1:7">
-      <c r="A47" s="35" t="s">
+      <c r="A47" s="28" t="s">
         <v>115</v>
       </c>
-      <c r="B47" s="48" t="s">
+      <c r="B47" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="C47" s="84" t="s">
+      <c r="C47" s="42" t="s">
         <v>109</v>
       </c>
-      <c r="D47" s="48" t="s">
+      <c r="D47" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="E47" s="83" t="s">
+      <c r="E47" s="42" t="s">
         <v>118</v>
       </c>
-      <c r="F47" s="83" t="s">
+      <c r="F47" s="42" t="s">
         <v>119</v>
       </c>
-      <c r="G47" s="55"/>
+      <c r="G47" s="37"/>
     </row>
     <row r="48" ht="51.75" spans="1:7">
-      <c r="A48" s="41"/>
-      <c r="B48" s="50"/>
-      <c r="C48" s="53"/>
-      <c r="D48" s="50"/>
-      <c r="E48" s="86" t="s">
+      <c r="A48" s="33"/>
+      <c r="B48" s="17"/>
+      <c r="C48" s="16"/>
+      <c r="D48" s="17"/>
+      <c r="E48" s="44" t="s">
         <v>120</v>
       </c>
-      <c r="F48" s="86" t="s">
+      <c r="F48" s="44" t="s">
         <v>121</v>
       </c>
-      <c r="G48" s="58"/>
+      <c r="G48" s="39"/>
     </row>
   </sheetData>
   <mergeCells count="64">
@@ -3028,60 +2941,187 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="1" outlineLevelCol="6"/>
+  <dimension ref="A1:G12"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="9.8984375" style="1" customWidth="1"/>
     <col min="2" max="2" width="16.015625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="17.5703125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="23.3046875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="27.2109375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="16.015625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="15.625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17.5703125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="23.3046875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="30.3359375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="16.015625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="15.625" style="2" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:7">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" ht="219" spans="1:5">
-      <c r="A2" s="1" t="s">
+    <row r="2" ht="108" customHeight="1" spans="1:5">
+      <c r="A2" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="C2" s="107" t="s">
+      <c r="C2" s="43" t="s">
         <v>124</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="E2" s="107" t="s">
+      <c r="E2" s="43" t="s">
         <v>126</v>
       </c>
     </row>
+    <row r="3" ht="219" spans="4:5">
+      <c r="D3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="E3" s="43" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="4" ht="34" spans="1:7">
+      <c r="A4" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="C4" s="43" t="s">
+        <v>131</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="E4" s="43" t="s">
+        <v>133</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="5" ht="168" spans="1:5">
+      <c r="A5" s="5"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E5" s="43" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="6" ht="51" spans="1:5">
+      <c r="A6" s="5"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E6" s="43" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="7" ht="51" spans="1:5">
+      <c r="A7" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="C7" s="54" t="s">
+        <v>141</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E7" s="43" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="8" ht="51" spans="1:5">
+      <c r="A8" s="5"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8" s="43" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="9" ht="34" spans="1:5">
+      <c r="A9" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C9" s="43" t="s">
+        <v>146</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E9" s="43" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="10" ht="34" spans="4:5">
+      <c r="D10" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="E10" s="43" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="11" ht="17" spans="4:5">
+      <c r="D11" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E11" s="43" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="12" ht="51" spans="4:5">
+      <c r="D12" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E12" s="43" t="s">
+        <v>144</v>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="C4:C6"/>
+    <mergeCell ref="C7:C8"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>

--- a/Doc_app/Test_case_ME_IOS.xlsx
+++ b/Doc_app/Test_case_ME_IOS.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="160">
   <si>
     <t>ID</t>
   </si>
@@ -534,7 +534,30 @@
     <t>F_BE_INS__IMG_01</t>
   </si>
   <si>
-    <t>kiểm tra khả năng insert Image layer mới</t>
+    <r>
+      <t xml:space="preserve">kiểm tra khả năng insert </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Image </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>mới</t>
+    </r>
   </si>
   <si>
     <t>- màn "Basic Edit"
@@ -554,7 +577,7 @@
     <t>F_BE_INS_IMG_02</t>
   </si>
   <si>
-    <t xml:space="preserve">- màn "Basic Edit" </t>
+    <t xml:space="preserve"> - các case này không thể thực hiện trên bản Android do sheet "Add Image" không có button "Camera" và button "Image" </t>
   </si>
   <si>
     <t>2. tap button "Camera"</t>
@@ -570,6 +593,30 @@
   </si>
   <si>
     <t>4. xác nhận sử dụng ảnh</t>
+  </si>
+  <si>
+    <t>FE_BE_INS_IMG_03</t>
+  </si>
+  <si>
+    <t>2. tap button "Image"</t>
+  </si>
+  <si>
+    <t>- popup dialog Gallary của OS</t>
+  </si>
+  <si>
+    <t>FE_BE_INS_IMG_04</t>
+  </si>
+  <si>
+    <t>1. chọn (tap) 1 ảnh bất kỳ trong mục "Recent Image"</t>
+  </si>
+  <si>
+    <t>FE_BE_INS_IMG_05</t>
+  </si>
+  <si>
+    <t>1. tap button "View all" của mục "Recent Image"</t>
+  </si>
+  <si>
+    <t>2. chọn 1 album bất kỳ</t>
   </si>
 </sst>
 </file>
@@ -582,7 +629,7 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="44" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -732,6 +779,14 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1399,7 +1454,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1416,6 +1471,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2133,659 +2191,659 @@
       <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="7" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:7">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="36"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="37"/>
     </row>
     <row r="3" ht="17" spans="1:7">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="42" t="s">
+      <c r="C3" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="42" t="s">
+      <c r="E3" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="42" t="s">
+      <c r="F3" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="37"/>
+      <c r="G3" s="38"/>
     </row>
     <row r="4" ht="135" customHeight="1" spans="1:7">
-      <c r="A4" s="13"/>
-      <c r="D4" s="14" t="s">
+      <c r="A4" s="14"/>
+      <c r="D4" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="43" t="s">
+      <c r="E4" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="38"/>
+      <c r="G4" s="39"/>
     </row>
     <row r="5" ht="34" spans="1:7">
-      <c r="A5" s="13"/>
-      <c r="D5" s="14" t="s">
+      <c r="A5" s="14"/>
+      <c r="D5" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="43" t="s">
+      <c r="E5" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="G5" s="38"/>
+      <c r="G5" s="39"/>
     </row>
     <row r="6" ht="101.75" spans="1:7">
-      <c r="A6" s="15"/>
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="17" t="s">
+      <c r="A6" s="16"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="44" t="s">
+      <c r="E6" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="F6" s="16"/>
-      <c r="G6" s="39"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="40"/>
     </row>
     <row r="7" ht="17.55" spans="1:7">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="19"/>
-      <c r="C7" s="20"/>
-      <c r="D7" s="19"/>
-      <c r="E7" s="19"/>
-      <c r="F7" s="19"/>
-      <c r="G7" s="40"/>
+      <c r="B7" s="20"/>
+      <c r="C7" s="21"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="20"/>
+      <c r="G7" s="41"/>
     </row>
     <row r="8" ht="103" customHeight="1" spans="1:7">
-      <c r="A8" s="18" t="s">
+      <c r="A8" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="45" t="s">
+      <c r="C8" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="22" t="s">
+      <c r="D8" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="E8" s="46" t="s">
+      <c r="E8" s="47" t="s">
         <v>25</v>
       </c>
-      <c r="F8" s="27"/>
-      <c r="G8" s="41"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="42"/>
     </row>
     <row r="9" ht="185" spans="1:7">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="23" t="s">
+      <c r="B9" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="42" t="s">
+      <c r="C9" s="43" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="E9" s="47" t="s">
+      <c r="E9" s="48" t="s">
         <v>29</v>
       </c>
-      <c r="F9" s="11"/>
-      <c r="G9" s="37"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="38"/>
     </row>
     <row r="10" ht="51.75" spans="1:7">
-      <c r="A10" s="15"/>
-      <c r="B10" s="24"/>
-      <c r="C10" s="16"/>
-      <c r="D10" s="17" t="s">
+      <c r="A10" s="16"/>
+      <c r="B10" s="25"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="E10" s="48" t="s">
+      <c r="E10" s="49" t="s">
         <v>31</v>
       </c>
-      <c r="F10" s="16"/>
-      <c r="G10" s="39"/>
+      <c r="F10" s="17"/>
+      <c r="G10" s="40"/>
     </row>
     <row r="11" ht="202" spans="1:7">
-      <c r="A11" s="10" t="s">
+      <c r="A11" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="B11" s="23" t="s">
+      <c r="B11" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="42" t="s">
+      <c r="C11" s="43" t="s">
         <v>23</v>
       </c>
-      <c r="D11" s="12" t="s">
+      <c r="D11" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="E11" s="47" t="s">
+      <c r="E11" s="48" t="s">
         <v>29</v>
       </c>
-      <c r="F11" s="11"/>
-      <c r="G11" s="49" t="s">
+      <c r="F11" s="12"/>
+      <c r="G11" s="50" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="12" ht="101" spans="1:7">
-      <c r="A12" s="13"/>
-      <c r="B12" s="25"/>
-      <c r="D12" s="14" t="s">
+      <c r="A12" s="14"/>
+      <c r="B12" s="26"/>
+      <c r="D12" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="E12" s="50" t="s">
+      <c r="E12" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="F12" s="43" t="s">
+      <c r="F12" s="44" t="s">
         <v>37</v>
       </c>
-      <c r="G12" s="38"/>
+      <c r="G12" s="39"/>
     </row>
     <row r="13" ht="34.75" spans="1:7">
-      <c r="A13" s="15"/>
-      <c r="B13" s="25"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="48" t="s">
+      <c r="A13" s="16"/>
+      <c r="B13" s="26"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="49" t="s">
         <v>38</v>
       </c>
-      <c r="F13" s="44" t="s">
+      <c r="F13" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="G13" s="39"/>
+      <c r="G13" s="40"/>
     </row>
     <row r="14" ht="34" spans="1:7">
-      <c r="A14" s="10" t="s">
+      <c r="A14" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="B14" s="25"/>
-      <c r="C14" s="42" t="s">
+      <c r="B14" s="26"/>
+      <c r="C14" s="43" t="s">
         <v>23</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="E14" s="47" t="s">
+      <c r="E14" s="48" t="s">
         <v>42</v>
       </c>
-      <c r="F14" s="11"/>
-      <c r="G14" s="49" t="s">
+      <c r="F14" s="12"/>
+      <c r="G14" s="50" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="15" ht="68" spans="1:7">
-      <c r="A15" s="13"/>
-      <c r="B15" s="25"/>
-      <c r="D15" s="14" t="s">
+      <c r="A15" s="14"/>
+      <c r="B15" s="26"/>
+      <c r="D15" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="E15" s="50" t="s">
+      <c r="E15" s="51" t="s">
         <v>44</v>
       </c>
-      <c r="F15" s="43" t="s">
+      <c r="F15" s="44" t="s">
         <v>37</v>
       </c>
-      <c r="G15" s="38"/>
+      <c r="G15" s="39"/>
     </row>
     <row r="16" ht="34.75" spans="1:7">
-      <c r="A16" s="15"/>
-      <c r="B16" s="25"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="48" t="s">
+      <c r="A16" s="16"/>
+      <c r="B16" s="26"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="49" t="s">
         <v>38</v>
       </c>
-      <c r="F16" s="44" t="s">
+      <c r="F16" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="G16" s="39"/>
+      <c r="G16" s="40"/>
     </row>
     <row r="17" ht="51" spans="1:7">
-      <c r="A17" s="10" t="s">
+      <c r="A17" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="B17" s="25"/>
-      <c r="C17" s="42" t="s">
+      <c r="B17" s="26"/>
+      <c r="C17" s="43" t="s">
         <v>23</v>
       </c>
-      <c r="D17" s="12" t="s">
+      <c r="D17" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="E17" s="47" t="s">
+      <c r="E17" s="48" t="s">
         <v>47</v>
       </c>
-      <c r="F17" s="11"/>
-      <c r="G17" s="49" t="s">
+      <c r="F17" s="12"/>
+      <c r="G17" s="50" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="18" ht="17" spans="1:7">
-      <c r="A18" s="13"/>
-      <c r="B18" s="25"/>
-      <c r="D18" s="14" t="s">
+      <c r="A18" s="14"/>
+      <c r="B18" s="26"/>
+      <c r="D18" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="E18" s="50" t="s">
+      <c r="E18" s="51" t="s">
         <v>29</v>
       </c>
-      <c r="G18" s="38"/>
+      <c r="G18" s="39"/>
     </row>
     <row r="19" ht="51" spans="1:7">
-      <c r="A19" s="13"/>
-      <c r="B19" s="25"/>
-      <c r="D19" s="14" t="s">
+      <c r="A19" s="14"/>
+      <c r="B19" s="26"/>
+      <c r="D19" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="E19" s="50" t="s">
+      <c r="E19" s="51" t="s">
         <v>50</v>
       </c>
-      <c r="F19" s="43" t="s">
+      <c r="F19" s="44" t="s">
         <v>37</v>
       </c>
-      <c r="G19" s="38"/>
+      <c r="G19" s="39"/>
     </row>
     <row r="20" ht="34.75" spans="1:7">
-      <c r="A20" s="15"/>
-      <c r="B20" s="24"/>
-      <c r="C20" s="16"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="48" t="s">
+      <c r="A20" s="16"/>
+      <c r="B20" s="25"/>
+      <c r="C20" s="17"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="49" t="s">
         <v>51</v>
       </c>
-      <c r="F20" s="44" t="s">
+      <c r="F20" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="G20" s="39"/>
+      <c r="G20" s="40"/>
     </row>
     <row r="21" ht="185" spans="1:7">
-      <c r="A21" s="10" t="s">
+      <c r="A21" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="B21" s="12" t="s">
+      <c r="B21" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="C21" s="42" t="s">
+      <c r="C21" s="43" t="s">
         <v>23</v>
       </c>
-      <c r="D21" s="12" t="s">
+      <c r="D21" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="E21" s="47" t="s">
+      <c r="E21" s="48" t="s">
         <v>29</v>
       </c>
-      <c r="F21" s="11"/>
-      <c r="G21" s="37"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="38"/>
     </row>
     <row r="22" ht="101.75" spans="1:7">
-      <c r="A22" s="15"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="16"/>
-      <c r="D22" s="17" t="s">
+      <c r="A22" s="16"/>
+      <c r="B22" s="15"/>
+      <c r="C22" s="17"/>
+      <c r="D22" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="E22" s="48" t="s">
+      <c r="E22" s="49" t="s">
         <v>55</v>
       </c>
-      <c r="F22" s="16"/>
-      <c r="G22" s="39"/>
+      <c r="F22" s="17"/>
+      <c r="G22" s="40"/>
     </row>
     <row r="23" ht="101" spans="1:7">
-      <c r="A23" s="10" t="s">
+      <c r="A23" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="B23" s="14"/>
-      <c r="C23" s="42" t="s">
+      <c r="B23" s="15"/>
+      <c r="C23" s="43" t="s">
         <v>23</v>
       </c>
-      <c r="D23" s="12" t="s">
+      <c r="D23" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="E23" s="47" t="s">
+      <c r="E23" s="48" t="s">
         <v>29</v>
       </c>
-      <c r="F23" s="11"/>
-      <c r="G23" s="37"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="38"/>
     </row>
     <row r="24" ht="101.75" spans="1:7">
-      <c r="A24" s="15"/>
-      <c r="B24" s="17"/>
-      <c r="C24" s="16"/>
-      <c r="D24" s="17" t="s">
+      <c r="A24" s="16"/>
+      <c r="B24" s="18"/>
+      <c r="C24" s="17"/>
+      <c r="D24" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="E24" s="48" t="s">
+      <c r="E24" s="49" t="s">
         <v>58</v>
       </c>
-      <c r="F24" s="16"/>
-      <c r="G24" s="39"/>
+      <c r="F24" s="17"/>
+      <c r="G24" s="40"/>
     </row>
     <row r="25" ht="185" spans="1:7">
-      <c r="A25" s="10" t="s">
+      <c r="A25" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="B25" s="12" t="s">
+      <c r="B25" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="C25" s="42" t="s">
+      <c r="C25" s="43" t="s">
         <v>23</v>
       </c>
-      <c r="D25" s="12" t="s">
+      <c r="D25" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="E25" s="47" t="s">
+      <c r="E25" s="48" t="s">
         <v>29</v>
       </c>
-      <c r="F25" s="11"/>
-      <c r="G25" s="37"/>
+      <c r="F25" s="12"/>
+      <c r="G25" s="38"/>
     </row>
     <row r="26" ht="110" customHeight="1" spans="1:7">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="D26" s="14" t="s">
+      <c r="A26" s="14"/>
+      <c r="B26" s="15"/>
+      <c r="D26" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="E26" s="50" t="s">
+      <c r="E26" s="51" t="s">
         <v>62</v>
       </c>
-      <c r="F26" s="43" t="s">
+      <c r="F26" s="44" t="s">
         <v>37</v>
       </c>
-      <c r="G26" s="38"/>
+      <c r="G26" s="39"/>
     </row>
     <row r="27" ht="68.75" spans="1:7">
-      <c r="A27" s="15"/>
-      <c r="B27" s="17"/>
-      <c r="C27" s="16"/>
-      <c r="D27" s="17"/>
-      <c r="E27" s="48" t="s">
+      <c r="A27" s="16"/>
+      <c r="B27" s="18"/>
+      <c r="C27" s="17"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="49" t="s">
         <v>63</v>
       </c>
-      <c r="F27" s="44" t="s">
+      <c r="F27" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="G27" s="39"/>
+      <c r="G27" s="40"/>
     </row>
     <row r="28" ht="101.75" spans="1:7">
-      <c r="A28" s="18" t="s">
+      <c r="A28" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="B28" s="26" t="s">
+      <c r="B28" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="C28" s="51" t="s">
+      <c r="C28" s="52" t="s">
         <v>23</v>
       </c>
-      <c r="D28" s="22" t="s">
+      <c r="D28" s="23" t="s">
         <v>66</v>
       </c>
-      <c r="E28" s="51" t="s">
+      <c r="E28" s="52" t="s">
         <v>67</v>
       </c>
-      <c r="F28" s="27"/>
-      <c r="G28" s="41"/>
+      <c r="F28" s="28"/>
+      <c r="G28" s="42"/>
     </row>
     <row r="29" ht="152" spans="1:7">
-      <c r="A29" s="28" t="s">
+      <c r="A29" s="29" t="s">
         <v>68</v>
       </c>
-      <c r="B29" s="29" t="s">
+      <c r="B29" s="30" t="s">
         <v>69</v>
       </c>
-      <c r="C29" s="52" t="s">
+      <c r="C29" s="53" t="s">
         <v>23</v>
       </c>
-      <c r="D29" s="12" t="s">
+      <c r="D29" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="E29" s="42" t="s">
+      <c r="E29" s="43" t="s">
         <v>71</v>
       </c>
-      <c r="F29" s="52" t="s">
+      <c r="F29" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="G29" s="37"/>
+      <c r="G29" s="38"/>
     </row>
     <row r="30" ht="17" spans="1:7">
-      <c r="A30" s="31"/>
-      <c r="B30" s="32"/>
+      <c r="A30" s="32"/>
+      <c r="B30" s="33"/>
       <c r="C30" s="5"/>
-      <c r="D30" s="14" t="s">
+      <c r="D30" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="E30" s="43" t="s">
+      <c r="E30" s="44" t="s">
         <v>73</v>
       </c>
       <c r="F30" s="5"/>
-      <c r="G30" s="38" t="s">
+      <c r="G30" s="39" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="31" ht="84" spans="1:7">
-      <c r="A31" s="31"/>
-      <c r="B31" s="32"/>
+      <c r="A31" s="32"/>
+      <c r="B31" s="33"/>
       <c r="C31" s="5"/>
-      <c r="D31" s="14" t="s">
+      <c r="D31" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="E31" s="53" t="s">
+      <c r="E31" s="54" t="s">
         <v>76</v>
       </c>
       <c r="F31" s="5"/>
-      <c r="G31" s="38"/>
+      <c r="G31" s="39"/>
     </row>
     <row r="32" ht="84.75" spans="1:7">
-      <c r="A32" s="33"/>
-      <c r="B32" s="32"/>
-      <c r="C32" s="34"/>
-      <c r="D32" s="17" t="s">
+      <c r="A32" s="34"/>
+      <c r="B32" s="33"/>
+      <c r="C32" s="35"/>
+      <c r="D32" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="E32" s="44" t="s">
+      <c r="E32" s="45" t="s">
         <v>78</v>
       </c>
-      <c r="F32" s="34"/>
-      <c r="G32" s="39" t="s">
+      <c r="F32" s="35"/>
+      <c r="G32" s="40" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="33" ht="17" spans="1:7">
-      <c r="A33" s="31" t="s">
+      <c r="A33" s="32" t="s">
         <v>80</v>
       </c>
-      <c r="B33" s="32"/>
-      <c r="C33" s="54" t="s">
+      <c r="B33" s="33"/>
+      <c r="C33" s="55" t="s">
         <v>23</v>
       </c>
-      <c r="D33" s="14" t="s">
+      <c r="D33" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="E33" s="53" t="s">
+      <c r="E33" s="54" t="s">
         <v>29</v>
       </c>
-      <c r="F33" s="53" t="s">
+      <c r="F33" s="54" t="s">
         <v>82</v>
       </c>
-      <c r="G33" s="55" t="s">
+      <c r="G33" s="56" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="34" ht="84.75" spans="1:7">
-      <c r="A34" s="33"/>
-      <c r="B34" s="35"/>
-      <c r="C34" s="34"/>
-      <c r="D34" s="17" t="s">
+      <c r="A34" s="34"/>
+      <c r="B34" s="36"/>
+      <c r="C34" s="35"/>
+      <c r="D34" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="E34" s="44" t="s">
+      <c r="E34" s="45" t="s">
         <v>76</v>
       </c>
-      <c r="F34" s="16"/>
-      <c r="G34" s="39"/>
+      <c r="F34" s="17"/>
+      <c r="G34" s="40"/>
     </row>
     <row r="35" ht="185.75" spans="1:7">
-      <c r="A35" s="18" t="s">
+      <c r="A35" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="B35" s="23" t="s">
+      <c r="B35" s="24" t="s">
         <v>85</v>
       </c>
-      <c r="C35" s="51" t="s">
+      <c r="C35" s="52" t="s">
         <v>23</v>
       </c>
-      <c r="D35" s="22" t="s">
+      <c r="D35" s="23" t="s">
         <v>86</v>
       </c>
-      <c r="E35" s="51" t="s">
+      <c r="E35" s="52" t="s">
         <v>87</v>
       </c>
-      <c r="F35" s="27"/>
-      <c r="G35" s="41"/>
+      <c r="F35" s="28"/>
+      <c r="G35" s="42"/>
     </row>
     <row r="36" ht="17" spans="1:7">
-      <c r="A36" s="10" t="s">
+      <c r="A36" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="B36" s="25"/>
-      <c r="C36" s="42" t="s">
+      <c r="B36" s="26"/>
+      <c r="C36" s="43" t="s">
         <v>23</v>
       </c>
-      <c r="D36" s="12" t="s">
+      <c r="D36" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="E36" s="47" t="s">
+      <c r="E36" s="48" t="s">
         <v>29</v>
       </c>
-      <c r="F36" s="11"/>
-      <c r="G36" s="37"/>
-    </row>
-    <row r="37" s="7" customFormat="1" ht="51.75" spans="1:7">
-      <c r="A37" s="13"/>
-      <c r="B37" s="25"/>
+      <c r="F36" s="12"/>
+      <c r="G36" s="38"/>
+    </row>
+    <row r="37" s="8" customFormat="1" ht="51.75" spans="1:7">
+      <c r="A37" s="14"/>
+      <c r="B37" s="26"/>
       <c r="C37" s="2"/>
-      <c r="D37" s="17" t="s">
+      <c r="D37" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="E37" s="48" t="s">
+      <c r="E37" s="49" t="s">
         <v>90</v>
       </c>
-      <c r="F37" s="16"/>
-      <c r="G37" s="39"/>
+      <c r="F37" s="17"/>
+      <c r="G37" s="40"/>
     </row>
     <row r="38" ht="152" spans="1:7">
-      <c r="A38" s="10" t="s">
+      <c r="A38" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="B38" s="23" t="s">
+      <c r="B38" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="C38" s="42" t="s">
+      <c r="C38" s="43" t="s">
         <v>23</v>
       </c>
-      <c r="D38" s="12" t="s">
+      <c r="D38" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="E38" s="42" t="s">
+      <c r="E38" s="43" t="s">
         <v>94</v>
       </c>
-      <c r="F38" s="42" t="s">
+      <c r="F38" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="G38" s="37"/>
+      <c r="G38" s="38"/>
     </row>
     <row r="39" ht="28" customHeight="1" spans="1:7">
-      <c r="A39" s="13"/>
-      <c r="B39" s="25"/>
-      <c r="D39" s="14" t="s">
+      <c r="A39" s="14"/>
+      <c r="B39" s="26"/>
+      <c r="D39" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="E39" s="43" t="s">
+      <c r="E39" s="44" t="s">
         <v>29</v>
       </c>
-      <c r="G39" s="38"/>
+      <c r="G39" s="39"/>
     </row>
     <row r="40" ht="71" customHeight="1" spans="1:7">
-      <c r="A40" s="15"/>
-      <c r="B40" s="25"/>
-      <c r="C40" s="16"/>
-      <c r="D40" s="17" t="s">
+      <c r="A40" s="16"/>
+      <c r="B40" s="26"/>
+      <c r="C40" s="17"/>
+      <c r="D40" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="E40" s="44" t="s">
+      <c r="E40" s="45" t="s">
         <v>96</v>
       </c>
-      <c r="F40" s="16"/>
-      <c r="G40" s="39"/>
+      <c r="F40" s="17"/>
+      <c r="G40" s="40"/>
     </row>
     <row r="41" ht="34" spans="1:7">
-      <c r="A41" s="31" t="s">
+      <c r="A41" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="B41" s="25"/>
-      <c r="C41" s="43" t="s">
+      <c r="B41" s="26"/>
+      <c r="C41" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="D41" s="14" t="s">
+      <c r="D41" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="E41" s="53" t="s">
+      <c r="E41" s="54" t="s">
         <v>29</v>
       </c>
-      <c r="F41" s="53" t="s">
+      <c r="F41" s="54" t="s">
         <v>99</v>
       </c>
-      <c r="G41" s="55" t="s">
+      <c r="G41" s="56" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="42" ht="83" customHeight="1" spans="1:7">
-      <c r="A42" s="33"/>
-      <c r="B42" s="24"/>
-      <c r="C42" s="16"/>
-      <c r="D42" s="17" t="s">
+      <c r="A42" s="34"/>
+      <c r="B42" s="25"/>
+      <c r="C42" s="17"/>
+      <c r="D42" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="E42" s="44" t="s">
+      <c r="E42" s="45" t="s">
         <v>96</v>
       </c>
-      <c r="F42" s="16"/>
-      <c r="G42" s="39"/>
+      <c r="F42" s="17"/>
+      <c r="G42" s="40"/>
     </row>
     <row r="43" ht="152.75" spans="1:7">
-      <c r="A43" s="18" t="s">
+      <c r="A43" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="B43" s="22" t="s">
+      <c r="B43" s="23" t="s">
         <v>102</v>
       </c>
-      <c r="C43" s="51" t="s">
+      <c r="C43" s="52" t="s">
         <v>103</v>
       </c>
-      <c r="D43" s="22" t="s">
+      <c r="D43" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="E43" s="51" t="s">
+      <c r="E43" s="52" t="s">
         <v>105</v>
       </c>
-      <c r="F43" s="27"/>
-      <c r="G43" s="41"/>
+      <c r="F43" s="28"/>
+      <c r="G43" s="42"/>
     </row>
     <row r="44" ht="17.55" spans="1:7">
       <c r="A44" s="5" t="s">
@@ -2799,72 +2857,72 @@
       <c r="G44" s="5"/>
     </row>
     <row r="45" ht="58" customHeight="1" spans="1:7">
-      <c r="A45" s="28" t="s">
+      <c r="A45" s="29" t="s">
         <v>107</v>
       </c>
-      <c r="B45" s="12" t="s">
+      <c r="B45" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="C45" s="42" t="s">
+      <c r="C45" s="43" t="s">
         <v>109</v>
       </c>
-      <c r="D45" s="12" t="s">
+      <c r="D45" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="E45" s="42" t="s">
+      <c r="E45" s="43" t="s">
         <v>111</v>
       </c>
-      <c r="F45" s="11"/>
-      <c r="G45" s="49" t="s">
+      <c r="F45" s="12"/>
+      <c r="G45" s="50" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="46" ht="100" customHeight="1" spans="1:7">
-      <c r="A46" s="33"/>
-      <c r="B46" s="17"/>
-      <c r="C46" s="16"/>
-      <c r="D46" s="17" t="s">
+      <c r="A46" s="34"/>
+      <c r="B46" s="18"/>
+      <c r="C46" s="17"/>
+      <c r="D46" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="E46" s="44" t="s">
+      <c r="E46" s="45" t="s">
         <v>114</v>
       </c>
-      <c r="F46" s="16"/>
-      <c r="G46" s="39"/>
+      <c r="F46" s="17"/>
+      <c r="G46" s="40"/>
     </row>
     <row r="47" ht="51" spans="1:7">
-      <c r="A47" s="28" t="s">
+      <c r="A47" s="29" t="s">
         <v>115</v>
       </c>
-      <c r="B47" s="12" t="s">
+      <c r="B47" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="C47" s="42" t="s">
+      <c r="C47" s="43" t="s">
         <v>109</v>
       </c>
-      <c r="D47" s="12" t="s">
+      <c r="D47" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="E47" s="42" t="s">
+      <c r="E47" s="43" t="s">
         <v>118</v>
       </c>
-      <c r="F47" s="42" t="s">
+      <c r="F47" s="43" t="s">
         <v>119</v>
       </c>
-      <c r="G47" s="37"/>
+      <c r="G47" s="38"/>
     </row>
     <row r="48" ht="51.75" spans="1:7">
-      <c r="A48" s="33"/>
-      <c r="B48" s="17"/>
-      <c r="C48" s="16"/>
-      <c r="D48" s="17"/>
-      <c r="E48" s="44" t="s">
+      <c r="A48" s="34"/>
+      <c r="B48" s="18"/>
+      <c r="C48" s="17"/>
+      <c r="D48" s="18"/>
+      <c r="E48" s="45" t="s">
         <v>120</v>
       </c>
-      <c r="F48" s="44" t="s">
+      <c r="F48" s="45" t="s">
         <v>121</v>
       </c>
-      <c r="G48" s="39"/>
+      <c r="G48" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="64">
@@ -2941,7 +2999,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="9.8984375" style="1" customWidth="1"/>
@@ -2973,7 +3031,7 @@
       <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="7" t="s">
         <v>6</v>
       </c>
     </row>
@@ -2984,13 +3042,13 @@
       <c r="B2" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="C2" s="43" t="s">
+      <c r="C2" s="44" t="s">
         <v>124</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="E2" s="43" t="s">
+      <c r="E2" s="44" t="s">
         <v>126</v>
       </c>
     </row>
@@ -2998,7 +3056,7 @@
       <c r="D3" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="E3" s="43" t="s">
+      <c r="E3" s="44" t="s">
         <v>128</v>
       </c>
     </row>
@@ -3009,13 +3067,13 @@
       <c r="B4" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="C4" s="43" t="s">
+      <c r="C4" s="44" t="s">
         <v>131</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="E4" s="43" t="s">
+      <c r="E4" s="44" t="s">
         <v>133</v>
       </c>
       <c r="G4" s="2" t="s">
@@ -3029,7 +3087,7 @@
       <c r="D5" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="E5" s="43" t="s">
+      <c r="E5" s="44" t="s">
         <v>136</v>
       </c>
     </row>
@@ -3040,87 +3098,177 @@
       <c r="D6" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="E6" s="43" t="s">
+      <c r="E6" s="44" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="7" ht="51" spans="1:5">
+    <row r="7" ht="17" spans="1:5">
       <c r="A7" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="C7" s="54" t="s">
+      <c r="C7" s="55" t="s">
         <v>141</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="E7" s="43" t="s">
+      <c r="E7" s="44" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="8" ht="51" spans="1:5">
       <c r="A8" s="5"/>
-      <c r="B8" s="5"/>
+      <c r="B8" s="6"/>
       <c r="C8" s="5"/>
       <c r="D8" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E8" s="43" t="s">
+      <c r="E8" s="44" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="9" ht="34" spans="1:5">
-      <c r="A9" s="1" t="s">
+    <row r="9" ht="17" spans="1:7">
+      <c r="A9" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="C9" s="43" t="s">
-        <v>146</v>
-      </c>
+      <c r="B9" s="6"/>
+      <c r="C9" s="5"/>
       <c r="D9" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="E9" s="43" t="s">
+      <c r="E9" s="44" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="10" ht="34" spans="4:5">
+      <c r="G9" s="55" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="10" ht="34" spans="1:7">
+      <c r="A10" s="5"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="5"/>
       <c r="D10" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="E10" s="43" t="s">
+      <c r="E10" s="44" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="11" ht="17" spans="4:5">
+      <c r="G10" s="5"/>
+    </row>
+    <row r="11" ht="17" spans="1:7">
+      <c r="A11" s="5"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="5"/>
       <c r="D11" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="E11" s="43" t="s">
+      <c r="E11" s="44" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="12" ht="51" spans="4:5">
+      <c r="G11" s="5"/>
+    </row>
+    <row r="12" ht="51" spans="1:7">
+      <c r="A12" s="5"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="5"/>
       <c r="D12" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="E12" s="43" t="s">
+      <c r="E12" s="44" t="s">
         <v>144</v>
       </c>
+      <c r="G12" s="5"/>
+    </row>
+    <row r="13" ht="34" spans="1:7">
+      <c r="A13" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="B13" s="6"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E13" s="44" t="s">
+        <v>143</v>
+      </c>
+      <c r="G13" s="5"/>
+    </row>
+    <row r="14" ht="17" spans="1:7">
+      <c r="A14" s="5"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="E14" s="44" t="s">
+        <v>154</v>
+      </c>
+      <c r="G14" s="5"/>
+    </row>
+    <row r="15" ht="51" spans="1:7">
+      <c r="A15" s="5"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E15" s="44" t="s">
+        <v>144</v>
+      </c>
+      <c r="G15" s="5"/>
+    </row>
+    <row r="16" ht="51" spans="1:5">
+      <c r="A16" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C16" s="44" t="s">
+        <v>141</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="E16" s="44" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="17" ht="51" spans="1:4">
+      <c r="A17" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="C17" s="44" t="s">
+        <v>141</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="18" ht="17" spans="4:4">
+      <c r="D18" s="2" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="19" ht="17" spans="4:4">
+      <c r="D19" s="2" t="s">
+        <v>49</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="12">
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A7:A8"/>
+    <mergeCell ref="A9:A12"/>
+    <mergeCell ref="A13:A15"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="B4:B6"/>
-    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="B7:B15"/>
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="C4:C6"/>
-    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="C7:C15"/>
+    <mergeCell ref="G9:G15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/Doc_app/Test_case_ME_IOS.xlsx
+++ b/Doc_app/Test_case_ME_IOS.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27320" windowHeight="9460" activeTab="1"/>
+    <workbookView windowWidth="27320" windowHeight="10420" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="HOME_H" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="162">
   <si>
     <t>ID</t>
   </si>
@@ -535,6 +535,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">kiểm tra khả năng insert </t>
     </r>
     <r>
@@ -616,7 +623,14 @@
     <t>1. tap button "View all" của mục "Recent Image"</t>
   </si>
   <si>
+    <t>- popup Gallary
+- ảnh, album được load đầy đủ</t>
+  </si>
+  <si>
     <t>2. chọn 1 album bất kỳ</t>
+  </si>
+  <si>
+    <t>- load thành công tất cả các ảnh trong album</t>
   </si>
 </sst>
 </file>
@@ -3052,7 +3066,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="3" ht="219" spans="4:5">
+    <row r="3" ht="202" spans="4:5">
       <c r="D3" s="2" t="s">
         <v>127</v>
       </c>
@@ -3083,7 +3097,6 @@
     <row r="5" ht="168" spans="1:5">
       <c r="A5" s="5"/>
       <c r="B5" s="5"/>
-      <c r="C5" s="2"/>
       <c r="D5" s="2" t="s">
         <v>135</v>
       </c>
@@ -3094,7 +3107,6 @@
     <row r="6" ht="51" spans="1:5">
       <c r="A6" s="5"/>
       <c r="B6" s="5"/>
-      <c r="C6" s="2"/>
       <c r="D6" s="2" t="s">
         <v>137</v>
       </c>
@@ -3182,7 +3194,7 @@
       </c>
       <c r="G12" s="5"/>
     </row>
-    <row r="13" ht="34" spans="1:7">
+    <row r="13" ht="17" spans="1:7">
       <c r="A13" s="5" t="s">
         <v>152</v>
       </c>
@@ -3224,9 +3236,7 @@
       <c r="A16" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="C16" s="44" t="s">
-        <v>141</v>
-      </c>
+      <c r="C16" s="5"/>
       <c r="D16" s="2" t="s">
         <v>156</v>
       </c>
@@ -3234,40 +3244,56 @@
         <v>144</v>
       </c>
     </row>
-    <row r="17" ht="51" spans="1:4">
-      <c r="A17" s="1" t="s">
+    <row r="17" ht="34" spans="1:5">
+      <c r="A17" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="C17" s="44" t="s">
-        <v>141</v>
-      </c>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
       <c r="D17" s="2" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="18" ht="17" spans="4:4">
+      <c r="E17" s="44" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="18" ht="34" spans="1:5">
+      <c r="A18" s="5"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
       <c r="D18" s="2" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="19" ht="17" spans="4:4">
+        <v>160</v>
+      </c>
+      <c r="E18" s="44" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="19" ht="51" spans="1:5">
+      <c r="A19" s="5"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
       <c r="D19" s="2" t="s">
         <v>49</v>
       </c>
+      <c r="E19" s="44" t="s">
+        <v>144</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="14">
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A7:A8"/>
     <mergeCell ref="A9:A12"/>
     <mergeCell ref="A13:A15"/>
+    <mergeCell ref="A17:A19"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="B4:B6"/>
     <mergeCell ref="B7:B15"/>
+    <mergeCell ref="B17:B19"/>
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="C4:C6"/>
-    <mergeCell ref="C7:C15"/>
+    <mergeCell ref="C7:C19"/>
     <mergeCell ref="G9:G15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Doc_app/Test_case_ME_IOS.xlsx
+++ b/Doc_app/Test_case_ME_IOS.xlsx
@@ -4,11 +4,12 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27320" windowHeight="10420" activeTab="1"/>
+    <workbookView windowWidth="27320" windowHeight="9460" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="HOME_H" sheetId="1" r:id="rId1"/>
     <sheet name="BASIC_EDIT_BE" sheetId="2" r:id="rId2"/>
+    <sheet name="LAYER_MANAGE_LM" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="167">
   <si>
     <t>ID</t>
   </si>
@@ -631,6 +632,21 @@
   </si>
   <si>
     <t>- load thành công tất cả các ảnh trong album</t>
+  </si>
+  <si>
+    <t>F_LM_INS_IMG_01</t>
+  </si>
+  <si>
+    <t>F_LM_INS_IMG_02</t>
+  </si>
+  <si>
+    <t>F_LM_INS_IMG_03</t>
+  </si>
+  <si>
+    <t>F_LM_INS_IMG_04</t>
+  </si>
+  <si>
+    <t>F_LM_INS_IMG_05</t>
   </si>
 </sst>
 </file>
@@ -1468,7 +1484,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1485,13 +1501,19 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2176,14 +2198,14 @@
   <dimension ref="A1:G48"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="7.546875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="11.5859375" style="2" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="2" customWidth="1"/>
-    <col min="4" max="4" width="29.5546875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="40.1015625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="13.015625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="12.109375" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="2"/>
+    <col min="1" max="1" width="7.546875" style="5" customWidth="1"/>
+    <col min="2" max="2" width="11.5859375" style="5" customWidth="1"/>
+    <col min="3" max="3" width="12.375" style="5" customWidth="1"/>
+    <col min="4" max="4" width="29.5546875" style="5" customWidth="1"/>
+    <col min="5" max="5" width="40.1015625" style="5" customWidth="1"/>
+    <col min="6" max="6" width="13.015625" style="5" customWidth="1"/>
+    <col min="7" max="7" width="12.109375" style="5" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1" spans="1:7">
@@ -2210,733 +2232,733 @@
       </c>
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:7">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="37"/>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="39"/>
     </row>
     <row r="3" ht="17" spans="1:7">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="43" t="s">
+      <c r="C3" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="43" t="s">
+      <c r="E3" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="43" t="s">
+      <c r="F3" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="38"/>
+      <c r="G3" s="40"/>
     </row>
     <row r="4" ht="135" customHeight="1" spans="1:7">
-      <c r="A4" s="14"/>
-      <c r="D4" s="15" t="s">
+      <c r="A4" s="16"/>
+      <c r="D4" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="44" t="s">
+      <c r="E4" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="39"/>
+      <c r="G4" s="41"/>
     </row>
     <row r="5" ht="34" spans="1:7">
-      <c r="A5" s="14"/>
-      <c r="D5" s="15" t="s">
+      <c r="A5" s="16"/>
+      <c r="D5" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="44" t="s">
+      <c r="E5" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="G5" s="39"/>
+      <c r="G5" s="41"/>
     </row>
     <row r="6" ht="101.75" spans="1:7">
-      <c r="A6" s="16"/>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="18" t="s">
+      <c r="A6" s="18"/>
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="45" t="s">
+      <c r="E6" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="F6" s="17"/>
-      <c r="G6" s="40"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="42"/>
     </row>
     <row r="7" ht="17.55" spans="1:7">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="20"/>
-      <c r="C7" s="21"/>
-      <c r="D7" s="20"/>
-      <c r="E7" s="20"/>
-      <c r="F7" s="20"/>
-      <c r="G7" s="41"/>
+      <c r="B7" s="22"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="22"/>
+      <c r="E7" s="22"/>
+      <c r="F7" s="22"/>
+      <c r="G7" s="43"/>
     </row>
     <row r="8" ht="103" customHeight="1" spans="1:7">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="46" t="s">
+      <c r="C8" s="48" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="23" t="s">
+      <c r="D8" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="E8" s="47" t="s">
+      <c r="E8" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="F8" s="28"/>
-      <c r="G8" s="42"/>
+      <c r="F8" s="30"/>
+      <c r="G8" s="44"/>
     </row>
     <row r="9" ht="185" spans="1:7">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="24" t="s">
+      <c r="B9" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="43" t="s">
+      <c r="C9" s="45" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="13" t="s">
+      <c r="D9" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="E9" s="48" t="s">
+      <c r="E9" s="50" t="s">
         <v>29</v>
       </c>
-      <c r="F9" s="12"/>
-      <c r="G9" s="38"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="40"/>
     </row>
     <row r="10" ht="51.75" spans="1:7">
-      <c r="A10" s="16"/>
-      <c r="B10" s="25"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="18" t="s">
+      <c r="A10" s="18"/>
+      <c r="B10" s="27"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="E10" s="49" t="s">
+      <c r="E10" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="F10" s="17"/>
-      <c r="G10" s="40"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="42"/>
     </row>
     <row r="11" ht="202" spans="1:7">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="B11" s="24" t="s">
+      <c r="B11" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="43" t="s">
+      <c r="C11" s="45" t="s">
         <v>23</v>
       </c>
-      <c r="D11" s="13" t="s">
+      <c r="D11" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="E11" s="48" t="s">
+      <c r="E11" s="50" t="s">
         <v>29</v>
       </c>
-      <c r="F11" s="12"/>
-      <c r="G11" s="50" t="s">
+      <c r="F11" s="14"/>
+      <c r="G11" s="52" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="12" ht="101" spans="1:7">
-      <c r="A12" s="14"/>
-      <c r="B12" s="26"/>
-      <c r="D12" s="15" t="s">
+      <c r="A12" s="16"/>
+      <c r="B12" s="28"/>
+      <c r="D12" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="E12" s="51" t="s">
+      <c r="E12" s="53" t="s">
         <v>36</v>
       </c>
-      <c r="F12" s="44" t="s">
+      <c r="F12" s="46" t="s">
         <v>37</v>
       </c>
-      <c r="G12" s="39"/>
+      <c r="G12" s="41"/>
     </row>
     <row r="13" ht="34.75" spans="1:7">
-      <c r="A13" s="16"/>
-      <c r="B13" s="26"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="49" t="s">
+      <c r="A13" s="18"/>
+      <c r="B13" s="28"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="51" t="s">
         <v>38</v>
       </c>
-      <c r="F13" s="45" t="s">
+      <c r="F13" s="47" t="s">
         <v>39</v>
       </c>
-      <c r="G13" s="40"/>
+      <c r="G13" s="42"/>
     </row>
     <row r="14" ht="34" spans="1:7">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="B14" s="26"/>
-      <c r="C14" s="43" t="s">
+      <c r="B14" s="28"/>
+      <c r="C14" s="45" t="s">
         <v>23</v>
       </c>
-      <c r="D14" s="13" t="s">
+      <c r="D14" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="E14" s="48" t="s">
+      <c r="E14" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="F14" s="12"/>
-      <c r="G14" s="50" t="s">
+      <c r="F14" s="14"/>
+      <c r="G14" s="52" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="15" ht="68" spans="1:7">
-      <c r="A15" s="14"/>
-      <c r="B15" s="26"/>
-      <c r="D15" s="15" t="s">
+      <c r="A15" s="16"/>
+      <c r="B15" s="28"/>
+      <c r="D15" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="E15" s="51" t="s">
+      <c r="E15" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="F15" s="44" t="s">
+      <c r="F15" s="46" t="s">
         <v>37</v>
       </c>
-      <c r="G15" s="39"/>
+      <c r="G15" s="41"/>
     </row>
     <row r="16" ht="34.75" spans="1:7">
-      <c r="A16" s="16"/>
-      <c r="B16" s="26"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="49" t="s">
+      <c r="A16" s="18"/>
+      <c r="B16" s="28"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="51" t="s">
         <v>38</v>
       </c>
-      <c r="F16" s="45" t="s">
+      <c r="F16" s="47" t="s">
         <v>39</v>
       </c>
-      <c r="G16" s="40"/>
+      <c r="G16" s="42"/>
     </row>
     <row r="17" ht="51" spans="1:7">
-      <c r="A17" s="11" t="s">
+      <c r="A17" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="B17" s="26"/>
-      <c r="C17" s="43" t="s">
+      <c r="B17" s="28"/>
+      <c r="C17" s="45" t="s">
         <v>23</v>
       </c>
-      <c r="D17" s="13" t="s">
+      <c r="D17" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="E17" s="48" t="s">
+      <c r="E17" s="50" t="s">
         <v>47</v>
       </c>
-      <c r="F17" s="12"/>
-      <c r="G17" s="50" t="s">
+      <c r="F17" s="14"/>
+      <c r="G17" s="52" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="18" ht="17" spans="1:7">
-      <c r="A18" s="14"/>
-      <c r="B18" s="26"/>
-      <c r="D18" s="15" t="s">
+      <c r="A18" s="16"/>
+      <c r="B18" s="28"/>
+      <c r="D18" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="E18" s="51" t="s">
+      <c r="E18" s="53" t="s">
         <v>29</v>
       </c>
-      <c r="G18" s="39"/>
+      <c r="G18" s="41"/>
     </row>
     <row r="19" ht="51" spans="1:7">
-      <c r="A19" s="14"/>
-      <c r="B19" s="26"/>
-      <c r="D19" s="15" t="s">
+      <c r="A19" s="16"/>
+      <c r="B19" s="28"/>
+      <c r="D19" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="E19" s="51" t="s">
+      <c r="E19" s="53" t="s">
         <v>50</v>
       </c>
-      <c r="F19" s="44" t="s">
+      <c r="F19" s="46" t="s">
         <v>37</v>
       </c>
-      <c r="G19" s="39"/>
+      <c r="G19" s="41"/>
     </row>
     <row r="20" ht="34.75" spans="1:7">
-      <c r="A20" s="16"/>
-      <c r="B20" s="25"/>
-      <c r="C20" s="17"/>
-      <c r="D20" s="18"/>
-      <c r="E20" s="49" t="s">
+      <c r="A20" s="18"/>
+      <c r="B20" s="27"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="51" t="s">
         <v>51</v>
       </c>
-      <c r="F20" s="45" t="s">
+      <c r="F20" s="47" t="s">
         <v>39</v>
       </c>
-      <c r="G20" s="40"/>
+      <c r="G20" s="42"/>
     </row>
     <row r="21" ht="185" spans="1:7">
-      <c r="A21" s="11" t="s">
+      <c r="A21" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="B21" s="13" t="s">
+      <c r="B21" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="C21" s="43" t="s">
+      <c r="C21" s="45" t="s">
         <v>23</v>
       </c>
-      <c r="D21" s="13" t="s">
+      <c r="D21" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="E21" s="48" t="s">
+      <c r="E21" s="50" t="s">
         <v>29</v>
       </c>
-      <c r="F21" s="12"/>
-      <c r="G21" s="38"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="40"/>
     </row>
     <row r="22" ht="101.75" spans="1:7">
-      <c r="A22" s="16"/>
-      <c r="B22" s="15"/>
-      <c r="C22" s="17"/>
-      <c r="D22" s="18" t="s">
+      <c r="A22" s="18"/>
+      <c r="B22" s="17"/>
+      <c r="C22" s="19"/>
+      <c r="D22" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="E22" s="49" t="s">
+      <c r="E22" s="51" t="s">
         <v>55</v>
       </c>
-      <c r="F22" s="17"/>
-      <c r="G22" s="40"/>
+      <c r="F22" s="19"/>
+      <c r="G22" s="42"/>
     </row>
     <row r="23" ht="101" spans="1:7">
-      <c r="A23" s="11" t="s">
+      <c r="A23" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="B23" s="15"/>
-      <c r="C23" s="43" t="s">
+      <c r="B23" s="17"/>
+      <c r="C23" s="45" t="s">
         <v>23</v>
       </c>
-      <c r="D23" s="13" t="s">
+      <c r="D23" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="E23" s="48" t="s">
+      <c r="E23" s="50" t="s">
         <v>29</v>
       </c>
-      <c r="F23" s="12"/>
-      <c r="G23" s="38"/>
+      <c r="F23" s="14"/>
+      <c r="G23" s="40"/>
     </row>
     <row r="24" ht="101.75" spans="1:7">
-      <c r="A24" s="16"/>
-      <c r="B24" s="18"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="18" t="s">
+      <c r="A24" s="18"/>
+      <c r="B24" s="20"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="E24" s="49" t="s">
+      <c r="E24" s="51" t="s">
         <v>58</v>
       </c>
-      <c r="F24" s="17"/>
-      <c r="G24" s="40"/>
+      <c r="F24" s="19"/>
+      <c r="G24" s="42"/>
     </row>
     <row r="25" ht="185" spans="1:7">
-      <c r="A25" s="11" t="s">
+      <c r="A25" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="B25" s="13" t="s">
+      <c r="B25" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="C25" s="43" t="s">
+      <c r="C25" s="45" t="s">
         <v>23</v>
       </c>
-      <c r="D25" s="13" t="s">
+      <c r="D25" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="E25" s="48" t="s">
+      <c r="E25" s="50" t="s">
         <v>29</v>
       </c>
-      <c r="F25" s="12"/>
-      <c r="G25" s="38"/>
+      <c r="F25" s="14"/>
+      <c r="G25" s="40"/>
     </row>
     <row r="26" ht="110" customHeight="1" spans="1:7">
-      <c r="A26" s="14"/>
-      <c r="B26" s="15"/>
-      <c r="D26" s="15" t="s">
+      <c r="A26" s="16"/>
+      <c r="B26" s="17"/>
+      <c r="D26" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="E26" s="51" t="s">
+      <c r="E26" s="53" t="s">
         <v>62</v>
       </c>
-      <c r="F26" s="44" t="s">
+      <c r="F26" s="46" t="s">
         <v>37</v>
       </c>
-      <c r="G26" s="39"/>
+      <c r="G26" s="41"/>
     </row>
     <row r="27" ht="68.75" spans="1:7">
-      <c r="A27" s="16"/>
-      <c r="B27" s="18"/>
-      <c r="C27" s="17"/>
-      <c r="D27" s="18"/>
-      <c r="E27" s="49" t="s">
+      <c r="A27" s="18"/>
+      <c r="B27" s="20"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="20"/>
+      <c r="E27" s="51" t="s">
         <v>63</v>
       </c>
-      <c r="F27" s="45" t="s">
+      <c r="F27" s="47" t="s">
         <v>39</v>
       </c>
-      <c r="G27" s="40"/>
+      <c r="G27" s="42"/>
     </row>
     <row r="28" ht="101.75" spans="1:7">
-      <c r="A28" s="19" t="s">
+      <c r="A28" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="B28" s="27" t="s">
+      <c r="B28" s="29" t="s">
         <v>65</v>
       </c>
-      <c r="C28" s="52" t="s">
+      <c r="C28" s="54" t="s">
         <v>23</v>
       </c>
-      <c r="D28" s="23" t="s">
+      <c r="D28" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="E28" s="52" t="s">
+      <c r="E28" s="54" t="s">
         <v>67</v>
       </c>
-      <c r="F28" s="28"/>
-      <c r="G28" s="42"/>
+      <c r="F28" s="30"/>
+      <c r="G28" s="44"/>
     </row>
     <row r="29" ht="152" spans="1:7">
-      <c r="A29" s="29" t="s">
+      <c r="A29" s="31" t="s">
         <v>68</v>
       </c>
-      <c r="B29" s="30" t="s">
+      <c r="B29" s="32" t="s">
         <v>69</v>
       </c>
-      <c r="C29" s="53" t="s">
+      <c r="C29" s="55" t="s">
         <v>23</v>
       </c>
-      <c r="D29" s="13" t="s">
+      <c r="D29" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="E29" s="43" t="s">
+      <c r="E29" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="F29" s="53" t="s">
+      <c r="F29" s="55" t="s">
         <v>13</v>
       </c>
-      <c r="G29" s="38"/>
+      <c r="G29" s="40"/>
     </row>
     <row r="30" ht="17" spans="1:7">
-      <c r="A30" s="32"/>
-      <c r="B30" s="33"/>
-      <c r="C30" s="5"/>
-      <c r="D30" s="15" t="s">
+      <c r="A30" s="34"/>
+      <c r="B30" s="35"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="E30" s="44" t="s">
+      <c r="E30" s="46" t="s">
         <v>73</v>
       </c>
-      <c r="F30" s="5"/>
-      <c r="G30" s="39" t="s">
+      <c r="F30" s="8"/>
+      <c r="G30" s="41" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="31" ht="84" spans="1:7">
-      <c r="A31" s="32"/>
-      <c r="B31" s="33"/>
-      <c r="C31" s="5"/>
-      <c r="D31" s="15" t="s">
+      <c r="A31" s="34"/>
+      <c r="B31" s="35"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="E31" s="54" t="s">
+      <c r="E31" s="56" t="s">
         <v>76</v>
       </c>
-      <c r="F31" s="5"/>
-      <c r="G31" s="39"/>
+      <c r="F31" s="8"/>
+      <c r="G31" s="41"/>
     </row>
     <row r="32" ht="84.75" spans="1:7">
-      <c r="A32" s="34"/>
-      <c r="B32" s="33"/>
-      <c r="C32" s="35"/>
-      <c r="D32" s="18" t="s">
+      <c r="A32" s="36"/>
+      <c r="B32" s="35"/>
+      <c r="C32" s="37"/>
+      <c r="D32" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="E32" s="45" t="s">
+      <c r="E32" s="47" t="s">
         <v>78</v>
       </c>
-      <c r="F32" s="35"/>
-      <c r="G32" s="40" t="s">
+      <c r="F32" s="37"/>
+      <c r="G32" s="42" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="33" ht="17" spans="1:7">
-      <c r="A33" s="32" t="s">
+      <c r="A33" s="34" t="s">
         <v>80</v>
       </c>
-      <c r="B33" s="33"/>
-      <c r="C33" s="55" t="s">
+      <c r="B33" s="35"/>
+      <c r="C33" s="57" t="s">
         <v>23</v>
       </c>
-      <c r="D33" s="15" t="s">
+      <c r="D33" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="E33" s="54" t="s">
+      <c r="E33" s="56" t="s">
         <v>29</v>
       </c>
-      <c r="F33" s="54" t="s">
+      <c r="F33" s="56" t="s">
         <v>82</v>
       </c>
-      <c r="G33" s="56" t="s">
+      <c r="G33" s="58" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="34" ht="84.75" spans="1:7">
-      <c r="A34" s="34"/>
-      <c r="B34" s="36"/>
-      <c r="C34" s="35"/>
-      <c r="D34" s="18" t="s">
+      <c r="A34" s="36"/>
+      <c r="B34" s="38"/>
+      <c r="C34" s="37"/>
+      <c r="D34" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="E34" s="45" t="s">
+      <c r="E34" s="47" t="s">
         <v>76</v>
       </c>
-      <c r="F34" s="17"/>
-      <c r="G34" s="40"/>
+      <c r="F34" s="19"/>
+      <c r="G34" s="42"/>
     </row>
     <row r="35" ht="185.75" spans="1:7">
-      <c r="A35" s="19" t="s">
+      <c r="A35" s="21" t="s">
         <v>84</v>
       </c>
-      <c r="B35" s="24" t="s">
+      <c r="B35" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="C35" s="52" t="s">
+      <c r="C35" s="54" t="s">
         <v>23</v>
       </c>
-      <c r="D35" s="23" t="s">
+      <c r="D35" s="25" t="s">
         <v>86</v>
       </c>
-      <c r="E35" s="52" t="s">
+      <c r="E35" s="54" t="s">
         <v>87</v>
       </c>
-      <c r="F35" s="28"/>
-      <c r="G35" s="42"/>
+      <c r="F35" s="30"/>
+      <c r="G35" s="44"/>
     </row>
     <row r="36" ht="17" spans="1:7">
-      <c r="A36" s="11" t="s">
+      <c r="A36" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="B36" s="26"/>
-      <c r="C36" s="43" t="s">
+      <c r="B36" s="28"/>
+      <c r="C36" s="45" t="s">
         <v>23</v>
       </c>
-      <c r="D36" s="13" t="s">
+      <c r="D36" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="E36" s="48" t="s">
+      <c r="E36" s="50" t="s">
         <v>29</v>
       </c>
-      <c r="F36" s="12"/>
-      <c r="G36" s="38"/>
-    </row>
-    <row r="37" s="8" customFormat="1" ht="51.75" spans="1:7">
-      <c r="A37" s="14"/>
-      <c r="B37" s="26"/>
-      <c r="C37" s="2"/>
-      <c r="D37" s="18" t="s">
+      <c r="F36" s="14"/>
+      <c r="G36" s="40"/>
+    </row>
+    <row r="37" s="10" customFormat="1" ht="51.75" spans="1:7">
+      <c r="A37" s="16"/>
+      <c r="B37" s="28"/>
+      <c r="C37" s="5"/>
+      <c r="D37" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="E37" s="49" t="s">
+      <c r="E37" s="51" t="s">
         <v>90</v>
       </c>
-      <c r="F37" s="17"/>
-      <c r="G37" s="40"/>
+      <c r="F37" s="19"/>
+      <c r="G37" s="42"/>
     </row>
     <row r="38" ht="152" spans="1:7">
-      <c r="A38" s="11" t="s">
+      <c r="A38" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="B38" s="24" t="s">
+      <c r="B38" s="26" t="s">
         <v>92</v>
       </c>
-      <c r="C38" s="43" t="s">
+      <c r="C38" s="45" t="s">
         <v>23</v>
       </c>
-      <c r="D38" s="13" t="s">
+      <c r="D38" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="E38" s="43" t="s">
+      <c r="E38" s="45" t="s">
         <v>94</v>
       </c>
-      <c r="F38" s="43" t="s">
+      <c r="F38" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="G38" s="38"/>
+      <c r="G38" s="40"/>
     </row>
     <row r="39" ht="28" customHeight="1" spans="1:7">
-      <c r="A39" s="14"/>
-      <c r="B39" s="26"/>
-      <c r="D39" s="15" t="s">
+      <c r="A39" s="16"/>
+      <c r="B39" s="28"/>
+      <c r="D39" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="E39" s="44" t="s">
+      <c r="E39" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="G39" s="39"/>
+      <c r="G39" s="41"/>
     </row>
     <row r="40" ht="71" customHeight="1" spans="1:7">
-      <c r="A40" s="16"/>
-      <c r="B40" s="26"/>
-      <c r="C40" s="17"/>
-      <c r="D40" s="18" t="s">
+      <c r="A40" s="18"/>
+      <c r="B40" s="28"/>
+      <c r="C40" s="19"/>
+      <c r="D40" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="E40" s="45" t="s">
+      <c r="E40" s="47" t="s">
         <v>96</v>
       </c>
-      <c r="F40" s="17"/>
-      <c r="G40" s="40"/>
+      <c r="F40" s="19"/>
+      <c r="G40" s="42"/>
     </row>
     <row r="41" ht="34" spans="1:7">
-      <c r="A41" s="32" t="s">
+      <c r="A41" s="34" t="s">
         <v>97</v>
       </c>
-      <c r="B41" s="26"/>
-      <c r="C41" s="44" t="s">
+      <c r="B41" s="28"/>
+      <c r="C41" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="D41" s="15" t="s">
+      <c r="D41" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="E41" s="54" t="s">
+      <c r="E41" s="56" t="s">
         <v>29</v>
       </c>
-      <c r="F41" s="54" t="s">
+      <c r="F41" s="56" t="s">
         <v>99</v>
       </c>
-      <c r="G41" s="56" t="s">
+      <c r="G41" s="58" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="42" ht="83" customHeight="1" spans="1:7">
-      <c r="A42" s="34"/>
-      <c r="B42" s="25"/>
-      <c r="C42" s="17"/>
-      <c r="D42" s="18" t="s">
+      <c r="A42" s="36"/>
+      <c r="B42" s="27"/>
+      <c r="C42" s="19"/>
+      <c r="D42" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="E42" s="45" t="s">
+      <c r="E42" s="47" t="s">
         <v>96</v>
       </c>
-      <c r="F42" s="17"/>
-      <c r="G42" s="40"/>
+      <c r="F42" s="19"/>
+      <c r="G42" s="42"/>
     </row>
     <row r="43" ht="152.75" spans="1:7">
-      <c r="A43" s="19" t="s">
+      <c r="A43" s="21" t="s">
         <v>101</v>
       </c>
-      <c r="B43" s="23" t="s">
+      <c r="B43" s="25" t="s">
         <v>102</v>
       </c>
-      <c r="C43" s="52" t="s">
+      <c r="C43" s="54" t="s">
         <v>103</v>
       </c>
-      <c r="D43" s="23" t="s">
+      <c r="D43" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="E43" s="52" t="s">
+      <c r="E43" s="54" t="s">
         <v>105</v>
       </c>
-      <c r="F43" s="28"/>
-      <c r="G43" s="42"/>
+      <c r="F43" s="30"/>
+      <c r="G43" s="44"/>
     </row>
     <row r="44" ht="17.55" spans="1:7">
-      <c r="A44" s="5" t="s">
+      <c r="A44" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="B44" s="5"/>
-      <c r="C44" s="5"/>
-      <c r="D44" s="5"/>
-      <c r="E44" s="5"/>
-      <c r="F44" s="5"/>
-      <c r="G44" s="5"/>
+      <c r="B44" s="8"/>
+      <c r="C44" s="8"/>
+      <c r="D44" s="8"/>
+      <c r="E44" s="8"/>
+      <c r="F44" s="8"/>
+      <c r="G44" s="8"/>
     </row>
     <row r="45" ht="58" customHeight="1" spans="1:7">
-      <c r="A45" s="29" t="s">
+      <c r="A45" s="31" t="s">
         <v>107</v>
       </c>
-      <c r="B45" s="13" t="s">
+      <c r="B45" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="C45" s="43" t="s">
+      <c r="C45" s="45" t="s">
         <v>109</v>
       </c>
-      <c r="D45" s="13" t="s">
+      <c r="D45" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="E45" s="43" t="s">
+      <c r="E45" s="45" t="s">
         <v>111</v>
       </c>
-      <c r="F45" s="12"/>
-      <c r="G45" s="50" t="s">
+      <c r="F45" s="14"/>
+      <c r="G45" s="52" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="46" ht="100" customHeight="1" spans="1:7">
-      <c r="A46" s="34"/>
-      <c r="B46" s="18"/>
-      <c r="C46" s="17"/>
-      <c r="D46" s="18" t="s">
+      <c r="A46" s="36"/>
+      <c r="B46" s="20"/>
+      <c r="C46" s="19"/>
+      <c r="D46" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="E46" s="45" t="s">
+      <c r="E46" s="47" t="s">
         <v>114</v>
       </c>
-      <c r="F46" s="17"/>
-      <c r="G46" s="40"/>
+      <c r="F46" s="19"/>
+      <c r="G46" s="42"/>
     </row>
     <row r="47" ht="51" spans="1:7">
-      <c r="A47" s="29" t="s">
+      <c r="A47" s="31" t="s">
         <v>115</v>
       </c>
-      <c r="B47" s="13" t="s">
+      <c r="B47" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="C47" s="43" t="s">
+      <c r="C47" s="45" t="s">
         <v>109</v>
       </c>
-      <c r="D47" s="13" t="s">
+      <c r="D47" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="E47" s="43" t="s">
+      <c r="E47" s="45" t="s">
         <v>118</v>
       </c>
-      <c r="F47" s="43" t="s">
+      <c r="F47" s="45" t="s">
         <v>119</v>
       </c>
-      <c r="G47" s="38"/>
+      <c r="G47" s="40"/>
     </row>
     <row r="48" ht="51.75" spans="1:7">
-      <c r="A48" s="34"/>
-      <c r="B48" s="18"/>
-      <c r="C48" s="17"/>
-      <c r="D48" s="18"/>
-      <c r="E48" s="45" t="s">
+      <c r="A48" s="36"/>
+      <c r="B48" s="20"/>
+      <c r="C48" s="19"/>
+      <c r="D48" s="20"/>
+      <c r="E48" s="47" t="s">
         <v>120</v>
       </c>
-      <c r="F48" s="45" t="s">
+      <c r="F48" s="47" t="s">
         <v>121</v>
       </c>
-      <c r="G48" s="40"/>
+      <c r="G48" s="42"/>
     </row>
   </sheetData>
   <mergeCells count="64">
@@ -3018,11 +3040,11 @@
   <cols>
     <col min="1" max="1" width="9.8984375" style="1" customWidth="1"/>
     <col min="2" max="2" width="16.015625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="17.5703125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="23.3046875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="30.3359375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="16.015625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="15.625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="17.5703125" style="5" customWidth="1"/>
+    <col min="4" max="4" width="23.3046875" style="5" customWidth="1"/>
+    <col min="5" max="5" width="30.3359375" style="5" customWidth="1"/>
+    <col min="6" max="6" width="16.015625" style="5" customWidth="1"/>
+    <col min="7" max="7" width="15.625" style="5" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -3050,232 +3072,232 @@
       </c>
     </row>
     <row r="2" ht="108" customHeight="1" spans="1:5">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="C2" s="44" t="s">
+      <c r="C2" s="46" t="s">
         <v>124</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="E2" s="44" t="s">
+      <c r="E2" s="46" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="3" ht="202" spans="4:5">
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="E3" s="44" t="s">
+      <c r="E3" s="46" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="4" ht="34" spans="1:7">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="C4" s="44" t="s">
+      <c r="C4" s="46" t="s">
         <v>131</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="E4" s="44" t="s">
+      <c r="E4" s="46" t="s">
         <v>133</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="5" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="5" ht="168" spans="1:5">
-      <c r="A5" s="5"/>
-      <c r="B5" s="5"/>
-      <c r="D5" s="2" t="s">
+      <c r="A5" s="8"/>
+      <c r="B5" s="8"/>
+      <c r="D5" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="E5" s="44" t="s">
+      <c r="E5" s="46" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="6" ht="51" spans="1:5">
-      <c r="A6" s="5"/>
-      <c r="B6" s="5"/>
-      <c r="D6" s="2" t="s">
+      <c r="A6" s="8"/>
+      <c r="B6" s="8"/>
+      <c r="D6" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="E6" s="44" t="s">
+      <c r="E6" s="46" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="7" ht="17" spans="1:5">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="C7" s="55" t="s">
+      <c r="C7" s="57" t="s">
         <v>141</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="E7" s="44" t="s">
+      <c r="E7" s="46" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="8" ht="51" spans="1:5">
-      <c r="A8" s="5"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="2" t="s">
+      <c r="A8" s="8"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E8" s="44" t="s">
+      <c r="E8" s="46" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="9" ht="17" spans="1:7">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="B9" s="6"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="2" t="s">
+      <c r="B9" s="9"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="E9" s="44" t="s">
+      <c r="E9" s="46" t="s">
         <v>143</v>
       </c>
-      <c r="G9" s="55" t="s">
+      <c r="G9" s="57" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="10" ht="34" spans="1:7">
-      <c r="A10" s="5"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="2" t="s">
+      <c r="A10" s="8"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="E10" s="44" t="s">
+      <c r="E10" s="46" t="s">
         <v>148</v>
       </c>
-      <c r="G10" s="5"/>
+      <c r="G10" s="8"/>
     </row>
     <row r="11" ht="17" spans="1:7">
-      <c r="A11" s="5"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="2" t="s">
+      <c r="A11" s="8"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="E11" s="44" t="s">
+      <c r="E11" s="46" t="s">
         <v>150</v>
       </c>
-      <c r="G11" s="5"/>
+      <c r="G11" s="8"/>
     </row>
     <row r="12" ht="51" spans="1:7">
-      <c r="A12" s="5"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="2" t="s">
+      <c r="A12" s="8"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="E12" s="44" t="s">
+      <c r="E12" s="46" t="s">
         <v>144</v>
       </c>
-      <c r="G12" s="5"/>
+      <c r="G12" s="8"/>
     </row>
     <row r="13" ht="17" spans="1:7">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="B13" s="6"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="2" t="s">
+      <c r="B13" s="9"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="E13" s="44" t="s">
+      <c r="E13" s="46" t="s">
         <v>143</v>
       </c>
-      <c r="G13" s="5"/>
+      <c r="G13" s="8"/>
     </row>
     <row r="14" ht="17" spans="1:7">
-      <c r="A14" s="5"/>
-      <c r="B14" s="6"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="2" t="s">
+      <c r="A14" s="8"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="E14" s="44" t="s">
+      <c r="E14" s="46" t="s">
         <v>154</v>
       </c>
-      <c r="G14" s="5"/>
+      <c r="G14" s="8"/>
     </row>
     <row r="15" ht="51" spans="1:7">
-      <c r="A15" s="5"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="2" t="s">
+      <c r="A15" s="8"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="E15" s="44" t="s">
+      <c r="E15" s="46" t="s">
         <v>144</v>
       </c>
-      <c r="G15" s="5"/>
+      <c r="G15" s="8"/>
     </row>
     <row r="16" ht="51" spans="1:5">
       <c r="A16" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="C16" s="5"/>
-      <c r="D16" s="2" t="s">
+      <c r="C16" s="8"/>
+      <c r="D16" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="E16" s="44" t="s">
+      <c r="E16" s="46" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="17" ht="34" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="2" t="s">
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="E17" s="44" t="s">
+      <c r="E17" s="46" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="18" ht="34" spans="1:5">
-      <c r="A18" s="5"/>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="2" t="s">
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="E18" s="44" t="s">
+      <c r="E18" s="46" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="19" ht="51" spans="1:5">
-      <c r="A19" s="5"/>
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="2" t="s">
+      <c r="A19" s="8"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="E19" s="44" t="s">
+      <c r="E19" s="46" t="s">
         <v>144</v>
       </c>
     </row>
@@ -3299,4 +3321,244 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="6"/>
+  <cols>
+    <col min="1" max="1" width="9" style="2"/>
+    <col min="2" max="2" width="16.796875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="16.6640625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="22.390625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="27.2109375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="18.75" style="2" customWidth="1"/>
+    <col min="7" max="7" width="13.53125" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="24" customHeight="1" spans="1:7">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" ht="26" customHeight="1" spans="1:7">
+      <c r="A2" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="C2" s="46" t="s">
+        <v>141</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="E2" s="46" t="s">
+        <v>143</v>
+      </c>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+    </row>
+    <row r="3" ht="51" spans="1:7">
+      <c r="A3" s="5"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" s="46" t="s">
+        <v>144</v>
+      </c>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+    </row>
+    <row r="4" ht="25" customHeight="1" spans="1:7">
+      <c r="A4" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="B4" s="6"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="E4" s="46" t="s">
+        <v>143</v>
+      </c>
+      <c r="F4" s="5"/>
+      <c r="G4" s="46" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="5" ht="34" spans="1:7">
+      <c r="A5" s="5"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="E5" s="46" t="s">
+        <v>148</v>
+      </c>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+    </row>
+    <row r="6" ht="29" customHeight="1" spans="1:7">
+      <c r="A6" s="5"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="E6" s="46" t="s">
+        <v>150</v>
+      </c>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+    </row>
+    <row r="7" ht="51" spans="1:7">
+      <c r="A7" s="5"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="E7" s="46" t="s">
+        <v>144</v>
+      </c>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+    </row>
+    <row r="8" ht="26" customHeight="1" spans="1:7">
+      <c r="A8" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="B8" s="6"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="E8" s="46" t="s">
+        <v>143</v>
+      </c>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+    </row>
+    <row r="9" ht="17" spans="1:7">
+      <c r="A9" s="5"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="E9" s="46" t="s">
+        <v>154</v>
+      </c>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+    </row>
+    <row r="10" ht="62" customHeight="1" spans="1:7">
+      <c r="A10" s="5"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="E10" s="46" t="s">
+        <v>144</v>
+      </c>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+    </row>
+    <row r="11" ht="51" spans="1:7">
+      <c r="A11" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="E11" s="46" t="s">
+        <v>144</v>
+      </c>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+    </row>
+    <row r="12" ht="45" customHeight="1" spans="1:7">
+      <c r="A12" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="E12" s="46" t="s">
+        <v>159</v>
+      </c>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+    </row>
+    <row r="13" ht="34" spans="1:7">
+      <c r="A13" s="5"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="E13" s="46" t="s">
+        <v>161</v>
+      </c>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+    </row>
+    <row r="14" ht="56" customHeight="1" spans="1:7">
+      <c r="A14" s="5"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="E14" s="46" t="s">
+        <v>144</v>
+      </c>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A10"/>
+    <mergeCell ref="A12:A14"/>
+    <mergeCell ref="B2:B10"/>
+    <mergeCell ref="B12:B14"/>
+    <mergeCell ref="C2:C14"/>
+    <mergeCell ref="G4:G10"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>